--- a/docs/workbook/emergent-energy-system-map.xlsx
+++ b/docs/workbook/emergent-energy-system-map.xlsx
@@ -5722,7 +5722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7706,6 +7706,1266 @@
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>work_items, work_item_assignments, tr_items, project_eng_approvals, project_eng_stages, eng_stage_templates, qc_item_instance, qc_template_item, qc_checklist, approvals, deliverables, ms_objects, project_info, users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Execution Dashboard (legacy)</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>/dashboard</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /dashboard is immediately redirected to /gates. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /gates.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Revenue (legacy)</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>/revenue</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /revenue is immediately redirected to /revenue-tracker. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /revenue-tracker.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>COS Control (legacy)</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>/cos-control</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /cos-control is immediately redirected to /cos. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /cos.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow Forecast (legacy)</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow-forecast</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /cashflow-forecast is immediately redirected to /cashflow. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /cashflow.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>My Tool (legacy)</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>/my-tool</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /my-tool is immediately redirected to /. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>My Tool / Week (legacy)</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>/my-tool/week</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /my-tool/week is immediately redirected to /my-work/calendar. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /my-work/calendar.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>My Tool / Backlog (legacy)</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>/my-tool/backlog</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /my-tool/backlog is immediately redirected to /my-work/tasks. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /my-work/tasks.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>My Tool / Settings (legacy)</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>/my-tool/settings</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /my-tool/settings is immediately redirected to /my-work/settings. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /my-work/settings.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>My Tool / Help (legacy)</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>/my-tool/help</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /my-tool/help is immediately redirected to /. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>My Tool / Meetings (legacy)</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>/my-tool/meetings</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /my-tool/meetings is immediately redirected to /my-work/meetings. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /my-work/meetings.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Company Priorities (legacy)</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>/company-priorities</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /company-priorities is immediately redirected to /priorities. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /priorities.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Admin (legacy)</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>/admin</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /admin is immediately redirected to /admin/control-center. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /admin/control-center.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Admin Legacy Utilities</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>/admin/legacy-utilities</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /admin/legacy-utilities is immediately redirected to /admin/control-center. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /admin/control-center.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Exceptions (legacy)</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>/exceptions</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /exceptions is immediately redirected to /gates/exceptions. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /gates/exceptions.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle (legacy)</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /project-lifecycle is immediately redirected to /lifecycle-board. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /lifecycle-board.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Command Center (legacy)</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>/command-center</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /command-center is immediately redirected to /my-work. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /my-work.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>SSEG (legacy)</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>/sseg</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /sseg is immediately redirected to /handover?tab=sseg. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /handover?tab=sseg.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Quality Dashboard (project, legacy)</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>/quality/dashboard</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /quality/dashboard is immediately redirected to /quality. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /quality.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>NCR List (legacy)</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>/quality/ncrs</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /quality/ncrs is immediately redirected to /quality. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /quality.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>NCR Detail (legacy)</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>/quality/ncr/:id</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /quality/ncr/:id is immediately redirected to /quality. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /quality.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Standups (alias)</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>/standups</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /standups is immediately redirected to /engineering/standup. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /engineering/standup.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Teams Chats (alias)</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>/teams/chats</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /teams/chats is immediately redirected to /my-work/teams. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /my-work/teams.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Collaboration Hub (alias)</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>/collaboration</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /collaboration is immediately redirected to /my-work. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /my-work.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Collaboration Email (alias)</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>/collaboration/email</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /collaboration/email is immediately redirected to /my-work/email. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /my-work/email.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Collaboration Teams (alias)</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>/collaboration/teams</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /collaboration/teams is immediately redirected to /my-work/teams. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /my-work/teams.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>My Work Approvals (alias)</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/approvals</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /my-work/approvals is immediately redirected to /my-work/tasks?source=approvals. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /my-work/tasks?source=approvals.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>PM Deliverables (retired)</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>/pm/deliverables</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /pm/deliverables is immediately redirected to /pm/approvals. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /pm/approvals.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Department Scores (alias)</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>/department-scores</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /department-scores is immediately redirected to /leaderboard?tab=departments. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /leaderboard?tab=departments.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Procurement (alias)</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>/procurement</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /procurement is immediately redirected to /execution-board. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /execution-board.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>HSE Compliance (alias)</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>/hse/compliance</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>(automatic on page load)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Legacy / alias URL. Any visit to /hse/compliance is immediately redirected to /hse?tab=compliance. Nothing is shown to the user and nothing is saved.</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Redirects to /hse?tab=compliance.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
         </is>
       </c>
     </row>

--- a/docs/workbook/emergent-energy-system-map.xlsx
+++ b/docs/workbook/emergent-energy-system-map.xlsx
@@ -5722,7 +5722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8966,6 +8966,1476 @@
       <c r="H77" s="2" t="inlineStr">
         <is>
           <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects-summary</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>On load, fetches the master directory of every project with all columns needed for the table (name, phase, kWp, PM, PD, % complete, financial headline, dates, RAG, priority, escalation state).</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Reads every project's live summary row.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Populates the main projects table.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>project_info, project_execution_state, project_plan, dashboard_project_metrics, derived_project_kpis, priority_projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pm-assignable-users</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>On load, fetches the list of users who can be assigned as a PM, used to populate the PM dropdown in each row.</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Reads users table filtered by PM-assignable role.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Populates the PM dropdown on each project row.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>users, role_permissions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>On load, fetches the active company priorities for the priority-filter dropdown.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Reads active priorities.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Populates the priority filter dropdown.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>mytool_company_priorities, priority_projects, priority_derived_metrics (view).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>(when priority filter selected) GET /api/priorities/:id</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>When you pick a specific priority from the filter, fetches that priority's detail so we can show only the projects linked to it.</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Reads one priority's details.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Filters the projects table to just this priority's linked projects.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>mytool_company_priorities, priority_projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>(when priority filter selected) GET /api/priorities/:id/detail</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Sibling call to the priority-filter fetch — pulls enriched detail (linked projects and metrics).</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Reads priority projects and metrics.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Feeds the priority-filter side panel.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>priority_projects, derived_project_kpis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>(per project row) GET /api/projects-summary/:projectName/latest-update</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>When you hover / open a project row, fetches the latest PM weekly update for that project so we can show the tooltip / expanded row.</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Reads the most recent weekly review for that project.</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Populates the row's latest-update tooltip.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>weekly_reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>(per project row) GET /api/project-plan/:projectName</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>When you expand a project row, fetches its project plan (tasks) so PMs can see task-level completion.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Reads the project plan / work items for that project.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Populates the expanded-row task list.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>work_items, project_plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>'Create Project' button</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Navigates to the Project Create wizard to start a brand-new project.</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Nothing on click.</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Goes to /project-create.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>None on click.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>'Export' button</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Exports the current (filtered) project list as a CSV / Excel file for sharing outside the app.</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Reads the already-loaded projects summary.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Triggers a browser download.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>None (pure export of already-loaded data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>'Active projects' tab (`tab-active-projects`)</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Switches the table to show only active (non-archived) projects.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Filters client-side, no new fetch.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders table.</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>'Archived projects' tab (`tab-archived-projects`)</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Switches the table to show only archived projects.</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Filters client-side.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders table.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Phase filter (`select-phase-filter`)</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Filters the table by project phase (Design, Construction, Commissioning, etc.).</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Filters client-side.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders table.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>PM filter (`select-pm-filter`)</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Filters the table by assigned PM.</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Filters client-side.</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders table.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>RAG filter (`select-rag-filter`)</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Filters by RAG status: Red / Amber / Green.</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Filters client-side.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders table.</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Search box (`input-search`)</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Free-text search across project names / codes / clients.</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Filters client-side.</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders table.</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Task search (`input-search-tasks`)</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>When a project row is expanded, free-text search inside that project's task list.</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Filters the expanded task list client-side.</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders expanded row.</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Saved view picker (`select-view`)</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Loads a saved column/filter/sort view.</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Switches the local view config.</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders table.</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>'Clear' button</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Resets all active filters to their defaults.</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Clears local filter state.</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders table.</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Edit project name (`input-edit-project-name`)</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Inline-edit of the project's display name.</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Queues an update to the project row.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Commits on PATCH /api/project-info/:id.</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>project_info (update).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Edit size kWp (`input-edit-size-kwp`)</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Inline-edit of the project's size in kWp.</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Queues an update.</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Commits on PATCH /api/project-info/:id.</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>project_info (update).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Edit phase (`select-edit-phase`)</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Inline change of the project's current phase.</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Queues a phase change.</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Commits on PATCH /api/project-info/:id.</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>project_info (update), project_phase_history (insert).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Edit PM assignment (`select-edit-pm`)</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Inline re-assignment of the PM owning the project.</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Queues a PM change.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Commits on PATCH /api/project-info/:projectInfoId/assign-pm.</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>project_info (update), project_team_members (insert/update), audit_events (insert).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Edit PD (`input-edit-pd`)</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Inline re-assignment of the PD owning the project.</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Queues a PD change.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Commits on PATCH /api/project-info/:id.</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>project_info (update).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Edit Construction Start date (`input-edit-construction-start`)</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Inline edit of the construction start date.</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Queues a date change.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Commits on PATCH /api/project-info/:id.</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>project_info (update).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Edit Commissioning date (`input-edit-commissioning`)</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Inline edit of the commissioning date.</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Queues a date change.</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Commits on PATCH /api/project-info/:id.</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>project_info (update).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Edit Client Handover date (`input-edit-client-handover`)</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Inline edit of the client handover date.</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Queues a date change.</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Commits on PATCH /api/project-info/:id.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>project_info (update).</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Edit O&amp;M Handover date (`input-edit-om-handover`)</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Inline edit of the operations &amp; maintenance handover date.</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Queues a date change.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Commits on PATCH /api/project-info/:id.</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>project_info (update).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>File upload (`input-file-upload`)</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Upload a financial close document (PDF / Excel) and attach it to the project.</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Sends the file to the financial-close upload endpoint.</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Triggers GET /api/financial-close/upload handling.</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>project_financial_reviews (insert), sp_files (insert).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>SharePoint link input (`input-sharepoint-link`)</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Paste a SharePoint link instead of uploading a file.</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Saves the link against the project.</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Commits on PATCH /api/project-info/:id.</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>project_links (insert), project_info (update).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Not-applicable reason (`input-na-reason`)</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>If financial close isn't applicable for a project, record the reason.</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Saves the reason against the project.</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Commits on PATCH /api/project-info/:id.</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>project_info (update).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Saved view name (`input-view-name`)</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Name for a new saved view when creating one.</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Saves the view locally / to user prefs.</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Updates local view list.</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>dashboard_preferences (update).</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Inline % complete edit (in expanded task row)</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Edits a task's % complete directly from the projects table.</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Submits an override to the project plan.</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/project-plan/overrides.</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>work_items (update), project_plan (update).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Escalate project (row action)</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Flags or un-flags a project as escalated.</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Posts an escalation change.</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/projects-summary/:id/escalation.</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>project_info (update), audit_events (insert).</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Project name link (each row)</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Opens the detail page for that project.</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Nothing on click.</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Goes to /project/:projectName.</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>None on click.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Projects (list)</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>PM chat icon (each row)</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Opens the Teams chat group linked to that project.</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Nothing on click.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Navigates to /my-work/teams (pre-filtered).</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>None on click.</t>
         </is>
       </c>
     </row>

--- a/docs/workbook/emergent-energy-system-map.xlsx
+++ b/docs/workbook/emergent-energy-system-map.xlsx
@@ -5722,7 +5722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10436,6 +10436,5928 @@
       <c r="H112" s="2" t="inlineStr">
         <is>
           <t>None on click.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/budget-baselines?projectId={projectInfoId}</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Detail screen calls /api/budget-baselines?projectId={projectInfoId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Detail page.</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-assignable-users</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Detail screen calls /api/pd-assignable-users to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Detail page.</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pm-assignable-users</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Detail screen calls /api/pm-assignable-users to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Detail page.</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects/{projectId}/priorities</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Detail screen calls /api/projects/{projectId}/priorities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Detail page.</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/roles/{encodeURIComponent(userRole)}</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Detail screen calls /api/roles/{encodeURIComponent(userRole)} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Detail page.</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/sites?projectId_lookup={projectInfoId}</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Detail screen calls /api/sites?projectId_lookup={projectInfoId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Detail page.</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/users</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Detail screen calls /api/users to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Detail page.</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>`button-add-eng-task` button</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>'Add eng task' button — triggers the 'add eng task' action on the Project Detail screen.</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>`button-cancel-eng-task` button</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>'Cancel eng task' button — triggers the 'cancel eng task' action on the Project Detail screen.</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>`button-cancel-generate` button</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>'Cancel generate' button — triggers the 'cancel generate' action on the Project Detail screen.</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-generate` button</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm generate' button — triggers the 'confirm generate' action on the Project Detail screen.</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>`button-generate-eng-tasks` button</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>'Generate eng tasks' button — triggers the 'generate eng tasks' action on the Project Detail screen.</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>`button-save-eng-task` button</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>'Save eng task' button — triggers the 'save eng task' action on the Project Detail screen.</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-eng-task` input</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new eng task'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-eng-task-desc` input</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new eng task desc'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-eng-task-due` input</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new eng task due'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>`select-new-eng-task-assignee` selector</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'new eng task assignee'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Project Detail</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>`select-new-eng-task-priority` selector</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'new eng task priority'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Project Create</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>/project-create</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/clients</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Create screen calls /api/clients to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Create page.</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Project Create</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>/project-create</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects/similar-names</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Create screen calls /api/projects/similar-names to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Create page.</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Project Create</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>/project-create</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>`button-create-another` button</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>'Create another' button — triggers the 'create another' action on the Project Create screen.</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Project Create</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>/project-create</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>`button-create-project` button</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>'Create project' button — triggers the 'create project' action on the Project Create screen.</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Project Create</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>/project-create</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>`button-go-portfolio` button</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>'Go portfolio' button — triggers the 'go portfolio' action on the Project Create screen.</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Project Create</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>/project-create</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>`input-location` input</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'location'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Project Create</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>/project-create</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>`input-project-code` input</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'project code'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Project Create</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>/project-create</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>`input-project-name` input</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'project name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Project Create</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>/project-create</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>`select-initial-phase` selector</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'initial phase'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Project Create</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>/project-create</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>`select-project-client` selector</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'project client'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/clients</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Lifecycle screen calls /api/clients to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Lifecycle page.</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/mytool/company-priorities</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Lifecycle screen calls /api/mytool/company-priorities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Lifecycle page.</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/mytool/company-priorities/{id}</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Lifecycle screen calls /api/mytool/company-priorities/{id} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Lifecycle page.</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd/clients</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Lifecycle screen calls /api/pd/clients to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Lifecycle page.</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Lifecycle screen calls /api/priorities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Lifecycle page.</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/project-lifecycle/workspace</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Project Lifecycle screen calls /api/project-lifecycle/workspace to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Project Lifecycle page.</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>`button-add-priority` button</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>'Add priority' button — triggers the 'add priority' action on the Project Lifecycle screen.</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>`button-client-overview-create-project` button</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>'Client overview create project' button — triggers the 'client overview create project' action on the Project Lifecycle screen.</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>`button-client-overview-open-clients` button</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>'Client overview open clients' button — triggers the 'client overview open clients' action on the Project Lifecycle screen.</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>`button-open-client-workspace` button</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>'Open client workspace' button — triggers the 'open client workspace' action on the Project Lifecycle screen.</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>`button-open-clients` button</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>'Open clients' button — triggers the 'open clients' action on the Project Lifecycle screen.</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>`button-open-lifecycle` button</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>'Open lifecycle' button — triggers the 'open lifecycle' action on the Project Lifecycle screen.</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>`button-open-project-create-from-client-workspace` button</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>'Open project create from client workspace' button — triggers the 'open project create from client workspace' action on the Project Lifecycle screen.</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>`button-open-project-list` button</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>'Open project list' button — triggers the 'open project list' action on the Project Lifecycle screen.</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>`button-open-stage-gate-engine` button</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>'Open stage gate engine' button — triggers the 'open stage gate engine' action on the Project Lifecycle screen.</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>`button-project-lifecycle-create-client` button</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>'Project lifecycle create client' button — triggers the 'project lifecycle create client' action on the Project Lifecycle screen.</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>`button-refresh-project-lifecycle` button</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>'Refresh project lifecycle' button — triggers the 'refresh project lifecycle' action on the Project Lifecycle screen.</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>`button-retry-project-lifecycle` button</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>'Retry project lifecycle' button — triggers the 'retry project lifecycle' action on the Project Lifecycle screen.</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>`button-save-priority` button</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>'Save priority' button — triggers the 'save priority' action on the Project Lifecycle screen.</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>`input-priority-department` input</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'priority department'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>`input-priority-description` input</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'priority description'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>`input-priority-due-date` input</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'priority due date'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>`input-priority-title` input</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'priority title'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>`input-project-lifecycle-new-client-name` input</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'project lifecycle new client name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>`input-project-lifecycle-search` input</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'project lifecycle search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>`select-priority-severity` selector</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'priority severity'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Project Lifecycle</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>/project-lifecycle</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>`select-priority-status` selector</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'priority status'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Project Stage Gate</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName/gate/:stageCode</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>`button-back-project-gate` button</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>'Back project gate' button — triggers the 'back project gate' action on the Project Stage Gate screen.</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Portfolios</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/portfolio-dashboard</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Portfolios screen calls /api/portfolio-dashboard to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Portfolios page.</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Portfolios</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/portfolio-dashboard?view={viewMode}</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Portfolios screen calls /api/portfolio-dashboard?view={viewMode} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Portfolios page.</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Portfolios</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/portfolios</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Portfolios screen calls /api/portfolios to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Portfolios page.</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Portfolios</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>`button-cancel-create` button</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>'Cancel create' button — triggers the 'cancel create' action on the Portfolios screen.</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Portfolios</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-create` button</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm create' button — triggers the 'confirm create' action on the Portfolios screen.</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Portfolios</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>`button-create-portfolio` button</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>'Create portfolio' button — triggers the 'create portfolio' action on the Portfolios screen.</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Portfolios</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>`button-create-portfolio-empty` button</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>'Create portfolio empty' button — triggers the 'create portfolio empty' action on the Portfolios screen.</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Portfolios</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>`input-portfolio-client` input</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'portfolio client'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Portfolios</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>`input-portfolio-description` input</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'portfolio description'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Portfolios</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>`input-portfolio-name` input</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'portfolio name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Portfolios</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>`input-search-portfolios` input</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'search portfolios'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Portfolios</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>`select-portfolio-owner` selector</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'portfolio owner'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Portfolios</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>`select-portfolio-status` selector</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'portfolio status'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/portfolios</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Portfolio Detail screen calls /api/portfolios to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Portfolio Detail page.</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/portfolios/{portfolioId}</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Portfolio Detail screen calls /api/portfolios/{portfolioId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Portfolio Detail page.</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/portfolios/{portfolioId}/assign-project</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Portfolio Detail screen calls /api/portfolios/{portfolioId}/assign-project to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Portfolio Detail page.</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/portfolios/{portfolioId}/available-projects</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Portfolio Detail screen calls /api/portfolios/{portfolioId}/available-projects to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Portfolio Detail page.</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/portfolios/{portfolioId}/key-dates</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Portfolio Detail screen calls /api/portfolios/{portfolioId}/key-dates to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Portfolio Detail page.</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/portfolios/{portfolioId}/move-project</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Portfolio Detail screen calls /api/portfolios/{portfolioId}/move-project to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Portfolio Detail page.</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/portfolios/{portfolioId}/remove-project/{projectId}</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Portfolio Detail screen calls /api/portfolios/{portfolioId}/remove-project/{projectId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Portfolio Detail page.</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/portfolios/{portfolioId}/rollout-plans</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Portfolio Detail screen calls /api/portfolios/{portfolioId}/rollout-plans to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Portfolio Detail page.</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/portfolios/{portfolioId}/rollups</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Portfolio Detail screen calls /api/portfolios/{portfolioId}/rollups to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Portfolio Detail page.</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects-summary</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Portfolio Detail screen calls /api/projects-summary to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Portfolio Detail page.</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>`button-add-phase` button</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>'Add phase' button — triggers the 'add phase' action on the Portfolio Detail screen.</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>`button-add-projects` button</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>'Add projects' button — triggers the 'add projects' action on the Portfolio Detail screen.</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>`button-back` button</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>'Back' button — triggers the 'back' action on the Portfolio Detail screen.</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>`button-create-rollout` button</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>'Create rollout' button — triggers the 'create rollout' action on the Portfolio Detail screen.</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>`button-edit-portfolio` button</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>'Edit portfolio' button — triggers the 'edit portfolio' action on the Portfolio Detail screen.</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>`button-plan-gantt-view` button</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>'Plan gantt view' button — triggers the 'plan gantt view' action on the Portfolio Detail screen.</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>`button-plan-table-view` button</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>'Plan table view' button — triggers the 'plan table view' action on the Portfolio Detail screen.</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>`button-save-edit` button</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>'Save edit' button — triggers the 'save edit' action on the Portfolio Detail screen.</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-client` input</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit client'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-description` input</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit description'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-name` input</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>`input-rollout-name` input</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'rollout name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>`input-rollout-notes` input</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'rollout notes'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>`input-search-assign` input</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'search assign'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>`select-edit-owner` selector</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'edit owner'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>`select-edit-status` selector</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'edit status'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>`tab-cashflow` tab</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Portfolio Detail view to the 'cashflow' tab.</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>`tab-engineering` tab</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Portfolio Detail view to the 'engineering' tab.</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>`tab-finance` tab</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Portfolio Detail view to the 'finance' tab.</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>`tab-projects` tab</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Portfolio Detail view to the 'projects' tab.</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>`tab-quality` tab</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Portfolio Detail view to the 'quality' tab.</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Detail</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>/portfolios/:id</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>`tab-rollout` tab</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Portfolio Detail view to the 'rollout' tab.</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>/clients</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects-summary</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Clients screen calls /api/projects-summary to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Clients page.</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>/clients</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>`button-cancel-assign` button</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>'Cancel assign' button — triggers the 'cancel assign' action on the Clients screen.</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>/clients</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>`button-cancel-create` button</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>'Cancel create' button — triggers the 'cancel create' action on the Clients screen.</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>/clients</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-assign` button</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm assign' button — triggers the 'confirm assign' action on the Clients screen.</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>/clients</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-create` button</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm create' button — triggers the 'confirm create' action on the Clients screen.</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>/clients</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>`button-new-client` button</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>'New client' button — triggers the 'new client' action on the Clients screen.</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>/clients</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-client-name` input</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new client name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>/clients</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>`input-search-assign-project` input</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'search assign project'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>/clients</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>`input-search-clients` input</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'search clients'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>/clients</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>`select-assign-project` selector</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'assign project'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Client Detail</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>/clients/:clientId</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects-summary</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Client Detail screen calls /api/projects-summary to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Client Detail page.</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Client Detail</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>/clients/:clientId</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>`button-assign-project` button</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>'Assign project' button — triggers the 'assign project' action on the Client Detail screen.</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Client Project Departments</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>/clients/:clientId/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd/tickets?projectId={projectId}</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Client Project Departments screen calls /api/pd/tickets?projectId={projectId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Client Project Departments page.</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Client Project Departments</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>/clients/:clientId/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects/{encodeURIComponent(project!.project_name)}/health-summary</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Client Project Departments screen calls /api/projects/{encodeURIComponent(project!.project_name)}/health-summary to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Client Project Departments page.</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Client Project Departments</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>/clients/:clientId/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/stage-lifecycle/{projectId}</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Client Project Departments screen calls /api/stage-lifecycle/{projectId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Client Project Departments page.</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Sites</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>/sites</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/clients</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Sites screen calls /api/clients to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Sites page.</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Sites</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>/sites</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/clients-list</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Sites screen calls /api/clients-list to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Sites page.</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Sites</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>/sites</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/sites</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Sites screen calls /api/sites to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Sites page.</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Sites</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>/sites</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/sites/{id}</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/sites/{id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Sites</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>/sites</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/sites</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/sites when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/counterparties/{selectedId}</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Counterparties screen calls /api/counterparties/{selectedId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Counterparties page.</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/counterparties/{selectedId}/contacts</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Counterparties screen calls /api/counterparties/{selectedId}/contacts to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Counterparties page.</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/counterparties/{selectedId}/contacts/{contactId}</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Counterparties screen calls /api/counterparties/{selectedId}/contacts/{contactId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Counterparties page.</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/counterparties/detail</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Counterparties screen calls /api/counterparties/detail to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Counterparties page.</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/counterparties/summary</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Counterparties screen calls /api/counterparties/summary to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Counterparties page.</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Counterparties screen calls /api/invoice-patterns to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Counterparties page.</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/procurement-analysis/pattern-stats</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Counterparties screen calls /api/procurement-analysis/pattern-stats to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Counterparties page.</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/procurement-analysis/run</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Counterparties screen calls /api/procurement-analysis/run to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Counterparties page.</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/detail</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Counterparties screen calls /api/subcontractor-dashboard/detail to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Counterparties page.</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/merge</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Counterparties screen calls /api/subcontractor-dashboard/merge to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Counterparties page.</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/overdue</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Counterparties screen calls /api/subcontractor-dashboard/overdue to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Counterparties page.</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/summary</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Counterparties screen calls /api/subcontractor-dashboard/summary to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Counterparties page.</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>`input-counterparty-search` input</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'counterparty search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>`select-counterparty-status` selector</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'counterparty status'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Counterparties</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>/counterparties</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>`select-counterparty-type` selector</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'counterparty type'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Opportunities</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>/opportunities</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/clients</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Opportunities screen calls /api/clients to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Opportunities page.</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Opportunities</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>/opportunities</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/clients-list-opp</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Opportunities screen calls /api/clients-list-opp to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Opportunities page.</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Opportunities</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>/opportunities</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/opportunities</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Opportunities screen calls /api/opportunities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Opportunities page.</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Opportunities</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>/opportunities</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/opportunities/{id}</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/opportunities/{id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Opportunities</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>/opportunities</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/opportunities</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/opportunities when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
         </is>
       </c>
     </row>

--- a/docs/workbook/emergent-energy-system-map.xlsx
+++ b/docs/workbook/emergent-energy-system-map.xlsx
@@ -5722,7 +5722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16356,6 +16356,1560 @@
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Dashboard</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>/engineering</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/mytool/company-priorities</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Dashboard screen calls /api/mytool/company-priorities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/eng/deliverables/{del.id}/acknowledge</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Tasks screen calls /api/eng/deliverables/{del.id}/acknowledge to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Tasks page.</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/eng/tasks/{task.id}/send-deliverable</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Tasks screen calls /api/eng/tasks/{task.id}/send-deliverable to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Tasks page.</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/eng/tasks/{task.id}/send-for-approval</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Tasks screen calls /api/eng/tasks/{task.id}/send-for-approval to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Tasks page.</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects-summary</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Tasks screen calls /api/projects-summary to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Tasks page.</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>`button-create-task` button</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>'Create task' button — triggers the 'create task' action on the Engineering Tasks screen.</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>`button-submit-task` button</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>'Submit task' button — triggers the 'submit task' action on the Engineering Tasks screen.</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>`input-comment` input</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'comment'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>`input-drawer-due-date` input</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'drawer due date'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>`input-drawer-start-date` input</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'drawer start date'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>`input-post-update` input</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'post update'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>`input-post-update-hold-reason` input</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'post update hold reason'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>`input-task-description` input</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'task description'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>`input-task-due` input</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'task due'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>`input-task-project` input</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'task project'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>`input-task-search` input</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'task search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>`input-task-title` input</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'task title'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>`select-deliverable-recipient` selector</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'deliverable recipient'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>`select-drawer-priority` selector</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'drawer priority'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>`select-drawer-project` selector</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'drawer project'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>`select-drawer-status` selector</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'drawer status'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>`select-post-update-blocked-type` selector</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'post update blocked type'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>`select-post-update-status` selector</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'post update status'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>`select-task-assignee` selector</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'task assignee'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Tasks</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/tasks</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>`select-task-priority` selector</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'task priority'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Standup</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>/engineering/standup</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/standups/schedules</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Standup screen calls /api/standups/schedules to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Standup page.</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Monthly Report</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>/reports/engineering/monthly</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/engineering/monthly</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Monthly Report screen calls /api/reports/engineering/monthly to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Monthly Report page.</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Monthly Report</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>/reports/engineering/monthly</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/engineering/monthly?month={month}</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Monthly Report screen calls /api/reports/engineering/monthly?month={month} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Monthly Report page.</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Monthly Report</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>/reports/engineering/monthly</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/engineering/monthly?month={prevMonth}</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Monthly Report screen calls /api/reports/engineering/monthly?month={prevMonth} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Monthly Report page.</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Monthly History</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>/reports/engineering/monthly/history</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/engineering/monthly/history</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Monthly History screen calls /api/reports/engineering/monthly/history to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Monthly History page.</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Monthly Compare</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>/reports/engineering/monthly/compare</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/engineering/monthly/compare</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Monthly Compare screen calls /api/reports/engineering/monthly/compare to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Monthly Compare page.</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Monthly Compare</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>/reports/engineering/monthly/compare</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/engineering/monthly/compare?monthA={monthA}&amp;monthB={monthB}</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Monthly Compare screen calls /api/reports/engineering/monthly/compare?monthA={monthA}&amp;monthB={monthB} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Monthly Compare page.</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Monthly Project</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>/reports/engineering/monthly/:month/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/engineering/monthly</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Monthly Project screen calls /api/reports/engineering/monthly to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Monthly Project page.</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Monthly Project</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>/reports/engineering/monthly/:month/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/engineering/monthly/{reportId}/drilldown?{q.toString()}</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Monthly Project screen calls /api/reports/engineering/monthly/{reportId}/drilldown?{q.toString()} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Monthly Project page.</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Monthly Project</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>/reports/engineering/monthly/:month/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/engineering/monthly/{reportId}/project/{projectId}</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Monthly Project screen calls /api/reports/engineering/monthly/{reportId}/project/{projectId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Monthly Project page.</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Monthly Project</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>/reports/engineering/monthly/:month/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/engineering/monthly/project</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Monthly Project screen calls /api/reports/engineering/monthly/project to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Monthly Project page.</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Monthly Project</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>/reports/engineering/monthly/:month/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/engineering/monthly?month={month}</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Engineering Monthly Project screen calls /api/reports/engineering/monthly?month={month} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Engineering Monthly Project page.</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
         <is>
           <t>See Data Sources sheet for the handler + tables.</t>
         </is>

--- a/docs/workbook/emergent-energy-system-map.xlsx
+++ b/docs/workbook/emergent-energy-system-map.xlsx
@@ -5722,7 +5722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H290"/>
+  <dimension ref="A1:H399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17910,6 +17910,4584 @@
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>PM Dashboard</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>/pm-dashboard</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-pm-handover/completed</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM Dashboard screen calls /api/pd-pm-handover/completed to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>PM Dashboard</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>/pm-dashboard</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>`tab-calendar` tab</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>Switches the PM Dashboard view to the 'calendar' tab.</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>PM Dashboard</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>/pm-dashboard</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>`tab-more-options` tab</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>Switches the PM Dashboard view to the 'more options' tab.</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>PM Dashboard</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>/pm-dashboard</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>`tab-overview` tab</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>Switches the PM Dashboard view to the 'overview' tab.</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>PM Dashboard</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>/pm-dashboard</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>`tab-priority` tab</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>Switches the PM Dashboard view to the 'priority' tab.</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Home</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pm-otg/projects</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM On-The-Go Home screen calls /api/pm-otg/projects to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM On-The-Go Home page.</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/commissioning/{itemId}</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM On-The-Go Project screen calls /api/commissioning/{itemId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM On-The-Go Project page.</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pm-otg/projects/{projectId}/{endpoint}</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM On-The-Go Project screen calls /api/pm-otg/projects/{projectId}/{endpoint} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM On-The-Go Project page.</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/procurement</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM On-The-Go Project screen calls /api/procurement to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM On-The-Go Project page.</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>`input-delay-days` input</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'delay days'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>`input-delay-description` input</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'delay description'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>`input-esc-description` input</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'esc description'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>`input-inv-amount` input</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'inv amount'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>`input-inv-number` input</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'inv number'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>`input-inv-po` input</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'inv po'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>`input-photo-caption` input</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'photo caption'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>`input-photo-event` input</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'photo event'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>`input-photo-file` input</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'photo file'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>`input-po-amount` input</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'po amount'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>`input-po-description` input</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'po description'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>`input-po-number` input</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'po number'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>`input-po-supplier` input</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'po supplier'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>`input-proc-cost` input</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'proc cost'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>`input-proc-date` input</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'proc date'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>`input-proc-description` input</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'proc description'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>`input-proc-title` input</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'proc title'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>`input-progress-notes` input</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'progress notes'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>`input-risk-description` input</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'risk description'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>`input-risk-mitigation` input</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'risk mitigation'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>`input-sv-date` input</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'sv date'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>`input-sv-notes` input</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'sv notes'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>`input-sv-photos` input</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'sv photos'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>`input-vo-amount` input</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'vo amount'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>`input-vo-description` input</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'vo description'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>`input-vo-justification` input</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'vo justification'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>`select-delay-impact` selector</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'delay impact'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>`select-esc-level` selector</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'esc level'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>`select-esc-urgency` selector</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'esc urgency'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>`select-proc-category` selector</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'proc category'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>`select-risk-severity` selector</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'risk severity'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>PM On-The-Go Project</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>/pm/on-the-go/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>`select-sv-weather` selector</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'sv weather'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>PM Handover Review</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>/pm/handover-review</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-pm-handover/submitted</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM Handover Review screen calls /api/pd-pm-handover/submitted to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM Handover Review page.</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>PM Monthly Report</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>/reports/pm/monthly</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/pm/monthly</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM Monthly Report screen calls /api/reports/pm/monthly to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM Monthly Report page.</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>PM Monthly Report</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>/reports/pm/monthly</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/pm/monthly/compare</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM Monthly Report screen calls /api/reports/pm/monthly/compare to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM Monthly Report page.</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>PM Monthly Report</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>/reports/pm/monthly</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/pm/monthly/compare?monthA={previousMonth}&amp;monthB={month}</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM Monthly Report screen calls /api/reports/pm/monthly/compare?monthA={previousMonth}&amp;monthB={month} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM Monthly Report page.</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>PM Monthly Report</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>/reports/pm/monthly</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/pm/monthly?month={month}</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM Monthly Report screen calls /api/reports/pm/monthly?month={month} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM Monthly Report page.</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>PM Monthly Report History</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>/reports/pm/monthly/history</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/pm/monthly/history</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM Monthly Report History screen calls /api/reports/pm/monthly/history to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM Monthly Report History page.</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>PM Monthly Report Compare</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>/reports/pm/monthly/compare</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/pm/monthly/compare</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM Monthly Report Compare screen calls /api/reports/pm/monthly/compare to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM Monthly Report Compare page.</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>PM Monthly Report Compare</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>/reports/pm/monthly/compare</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/pm/monthly/compare?monthA={monthA}&amp;monthB={monthB}</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM Monthly Report Compare screen calls /api/reports/pm/monthly/compare?monthA={monthA}&amp;monthB={monthB} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM Monthly Report Compare page.</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>PM Monthly Report Project</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>/reports/pm/monthly/:month/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/pm/monthly</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM Monthly Report Project screen calls /api/reports/pm/monthly to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM Monthly Report Project page.</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>PM Monthly Report Project</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>/reports/pm/monthly/:month/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/pm/monthly/{reportId}/drilldown?{q.toString()}</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM Monthly Report Project screen calls /api/reports/pm/monthly/{reportId}/drilldown?{q.toString()} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM Monthly Report Project page.</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>PM Monthly Report Project</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>/reports/pm/monthly/:month/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/pm/monthly/{reportId}/project/{projectId}</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM Monthly Report Project screen calls /api/reports/pm/monthly/{reportId}/project/{projectId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM Monthly Report Project page.</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>PM Monthly Report Project</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>/reports/pm/monthly/:month/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/pm/monthly/project</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM Monthly Report Project screen calls /api/reports/pm/monthly/project to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM Monthly Report Project page.</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>PM Monthly Report Project</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>/reports/pm/monthly/:month/project/:projectId</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/reports/pm/monthly?month={month}</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PM Monthly Report Project screen calls /api/reports/pm/monthly?month={month} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PM Monthly Report Project page.</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>PD Dashboard</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>/pd</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-pm-handover/control</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Dashboard screen calls /api/pd-pm-handover/control to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>PD Dashboard</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>/pd</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd/dashboard</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Dashboard screen calls /api/pd/dashboard to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>PD Dashboard</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>/pd</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd/pipeline</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Dashboard screen calls /api/pd/pipeline to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>PD Dashboard</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>/pd</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd/tickets</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Dashboard screen calls /api/pd/tickets to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>PD Dashboard</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>/pd</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>`link-handover-control` link</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>Navigates to the 'handover control' destination.</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>Nothing on click.</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>Varies — see source.</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>None on click.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>PD Dashboard</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>/pd</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>`link-view-all-tickets` link</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>Navigates to the 'view all tickets' destination.</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>Nothing on click.</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>Varies — see source.</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>None on click.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>PD Tickets</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd/tickets</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Tickets screen calls /api/pd/tickets to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Tickets page.</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd/clients</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Ticket Create screen calls /api/pd/clients to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Ticket Create page.</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd/dashboard</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Ticket Create screen calls /api/pd/dashboard to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Ticket Create page.</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd/projects/search</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Ticket Create screen calls /api/pd/projects/search to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Ticket Create page.</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd/tickets</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Ticket Create screen calls /api/pd/tickets to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Ticket Create page.</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd/users</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Ticket Create screen calls /api/pd/users to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Ticket Create page.</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects/similar-names</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Ticket Create screen calls /api/projects/similar-names to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Ticket Create page.</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>`input-battery-size` input</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'battery size'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>`input-client-search` input</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'client search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>`input-comments` input</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'comments'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>`input-due-date` input</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'due date'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>`input-gps` input</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'gps'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>`input-inspection-link` input</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'inspection link'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-client-name` input</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new client name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-project-name` input</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new project name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>`input-project-search` input</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'project search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>`input-site-name` input</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'site name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>`input-size-kwp` input</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'size kwp'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>`input-working-schedule` input</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'working schedule'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>`select-designer` selector</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'designer'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>`select-funding-type` selector</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'funding type'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>`select-priority` selector</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'priority'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>`select-province` selector</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'province'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Create</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/create</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>`select-request-type` selector</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'request type'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Detail</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/:id</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/eng/tasks</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Ticket Detail screen calls /api/eng/tasks to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Ticket Detail page.</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Detail</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/:id</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd/tickets</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Ticket Detail screen calls /api/pd/tickets to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Ticket Detail page.</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Detail</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/:id</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd/users</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Ticket Detail screen calls /api/pd/users to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Ticket Detail page.</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Detail</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/:id</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Ticket Detail screen calls /api/projects to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Ticket Detail page.</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Detail</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/:id</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-engineering-ticket-description` input</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new engineering ticket description'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Detail</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/:id</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-engineering-ticket-due-date` input</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new engineering ticket due date'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Detail</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/:id</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-engineering-ticket-title` input</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new engineering ticket title'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>PD Ticket Detail</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>/pd/tickets/:id</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>`link-to-project` link</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>Navigates to the 'to project' destination.</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>Nothing on click.</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>Varies — see source.</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>None on click.</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>PD Reports</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>/pd/reports</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd/reports</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD Reports screen calls /api/pd/reports to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD Reports page.</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>PD→PM Handover v2</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>/pd/handover/:projectId</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/lessons-learnt?projectType={encodeURIComponent(tabData.projectType)}&amp;limit=3</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD→PM Handover v2 screen calls /api/lessons-learnt?projectType={encodeURIComponent(tabData.projectType)}&amp;limit=3 to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD→PM Handover v2 page.</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>PD→PM Handover v2</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>/pd/handover/:projectId</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-pm-handover/{projectId}</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD→PM Handover v2 screen calls /api/pd-pm-handover/{projectId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD→PM Handover v2 page.</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>PD→PM Handover v2</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>/pd/handover/:projectId</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-pm-handover/{projectId}/accept</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD→PM Handover v2 screen calls /api/pd-pm-handover/{projectId}/accept to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD→PM Handover v2 page.</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>PD→PM Handover v2</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>/pd/handover/:projectId</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-pm-handover/{projectId}/draft</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD→PM Handover v2 screen calls /api/pd-pm-handover/{projectId}/draft to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD→PM Handover v2 page.</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>PD→PM Handover v2</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>/pd/handover/:projectId</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-pm-handover/{projectId}/pd-sign-off</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD→PM Handover v2 screen calls /api/pd-pm-handover/{projectId}/pd-sign-off to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD→PM Handover v2 page.</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>PD→PM Handover v2</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>/pd/handover/:projectId</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-pm-handover/{projectId}/pm-sign-off</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD→PM Handover v2 screen calls /api/pd-pm-handover/{projectId}/pm-sign-off to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD→PM Handover v2 page.</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>PD→PM Handover v2</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>/pd/handover/:projectId</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-pm-handover/{projectId}/reject</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD→PM Handover v2 screen calls /api/pd-pm-handover/{projectId}/reject to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD→PM Handover v2 page.</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>PD→PM Handover v2</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>/pd/handover/:projectId</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-pm-handover/{projectId}/stakeholders</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD→PM Handover v2 screen calls /api/pd-pm-handover/{projectId}/stakeholders to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD→PM Handover v2 page.</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>PD→PM Handover v2</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>/pd/handover/:projectId</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-pm-handover/{projectId}/stakeholders/{id}</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD→PM Handover v2 screen calls /api/pd-pm-handover/{projectId}/stakeholders/{id} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD→PM Handover v2 page.</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>PD→PM Handover v2</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>/pd/handover/:projectId</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-pm-handover/{projectId}/submit</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD→PM Handover v2 screen calls /api/pd-pm-handover/{projectId}/submit to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD→PM Handover v2 page.</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>PD→PM Handover v2</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>/pd/handover/:projectId</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-pm-handover/control</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD→PM Handover v2 screen calls /api/pd-pm-handover/control to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD→PM Handover v2 page.</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>PD→PM Handover v2</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>/pd/handover/:projectId</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects-summary</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PD→PM Handover v2 screen calls /api/projects-summary to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PD→PM Handover v2 page.</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>Handover Control</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>/handover-control</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pd-pm-handover/control</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Handover Control screen calls /api/pd-pm-handover/control to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Handover Control page.</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>Handover Dashboard</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>/handover</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/handover/packs</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Handover Dashboard screen calls /api/handover/packs to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Handover Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>Handover Dashboard</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>/handover</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/handover/sseg</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Handover Dashboard screen calls /api/handover/sseg to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Handover Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>Handover Dashboard</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>/handover</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/sseg-applications</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Handover Dashboard screen calls /api/sseg-applications to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Handover Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
         <is>
           <t>See Data Sources sheet for the handler + tables.</t>
         </is>

--- a/docs/workbook/emergent-energy-system-map.xlsx
+++ b/docs/workbook/emergent-energy-system-map.xlsx
@@ -5722,7 +5722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H399"/>
+  <dimension ref="A1:H546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -22488,6 +22488,6180 @@
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>DELETE {CASHFLOW_API_BASE}/available-payment</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>Sends a DELETE to {CASHFLOW_API_BASE}/available-payment when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>DELETE {CASHFLOW_API_BASE}/opening-balance</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>Sends a DELETE to {CASHFLOW_API_BASE}/opening-balance when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>DELETE {CASHFLOW_API_BASE}/opex-weekly</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>Sends a DELETE to {CASHFLOW_API_BASE}/opex-weekly when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects-summary</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Cashflow screen calls /api/projects-summary to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Cashflow page.</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>POST {CASHFLOW_API_BASE}/available-payment</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to {CASHFLOW_API_BASE}/available-payment when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>POST {CASHFLOW_API_BASE}/opening-balance</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to {CASHFLOW_API_BASE}/opening-balance when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>POST {CASHFLOW_API_BASE}/opex-budget</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to {CASHFLOW_API_BASE}/opex-budget when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>POST {CASHFLOW_API_BASE}/opex-weekly</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to {CASHFLOW_API_BASE}/opex-weekly when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>`button-avail-cancel` button</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>'Avail cancel' button — triggers the 'avail cancel' action on the Cashflow screen.</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>`button-avail-history-close` button</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>'Avail history close' button — triggers the 'avail history close' action on the Cashflow screen.</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>`button-avail-save` button</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>'Avail save' button — triggers the 'avail save' action on the Cashflow screen.</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>`button-clear-all-projects` button</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>'Clear all projects' button — triggers the 'clear all projects' action on the Cashflow screen.</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>`button-history-close` button</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>'History close' button — triggers the 'history close' action on the Cashflow screen.</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>`button-opex-budget` button</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>'Opex budget' button — triggers the 'opex budget' action on the Cashflow screen.</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>`button-opex-cancel` button</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>'Opex cancel' button — triggers the 'opex cancel' action on the Cashflow screen.</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>`button-opex-save` button</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>'Opex save' button — triggers the 'opex save' action on the Cashflow screen.</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>`button-toggle-detail` button</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>'Toggle detail' button — triggers the 'toggle detail' action on the Cashflow screen.</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>`input-avail-payment-reason` input</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'avail payment reason'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>`input-avail-payment-value` input</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'avail payment value'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>`select-project-filter` selector</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'project filter'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>Revenue Tracker</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>/revenue-tracker</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/revenue-tracker</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Revenue Tracker screen calls /api/revenue-tracker to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Revenue Tracker page.</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>Revenue Tracker</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>/revenue-tracker</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/revenue-tracker/month-detail</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Revenue Tracker screen calls /api/revenue-tracker/month-detail to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Revenue Tracker page.</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>Revenue Tracker</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>/revenue-tracker</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/tracker-monthly</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/tracker-monthly when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>Revenue Tracker</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>/revenue-tracker</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>`button-close-drawer` button</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>'Close drawer' button — triggers the 'close drawer' action on the Revenue Tracker screen.</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>Revenue Tracker</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>/revenue-tracker</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>`button-retry-revenue-tracker` button</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>'Retry revenue tracker' button — triggers the 'retry revenue tracker' action on the Revenue Tracker screen.</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>Revenue Tracker</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>/revenue-tracker</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>`input-search-detail` input</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'search detail'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>Revenue Tracker</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>/revenue-tracker</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>`select-project-filter` selector</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'project filter'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>Revenue Tracker</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>/revenue-tracker</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>`select-state-filter` selector</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'state filter'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>COS Tracker</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>/cos</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/cos-tracker</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>On load, the COS Tracker screen calls /api/cos-tracker to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the COS Tracker page.</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>COS Tracker</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>/cos</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/cos-tracker/month-detail</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>On load, the COS Tracker screen calls /api/cos-tracker/month-detail to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the COS Tracker page.</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>COS Tracker</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>/cos</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/cos-tracker/override-status/{id}</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/cos-tracker/override-status/{id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>COS Tracker</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>/cos</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/cos-tracker/toggle-realised/{id}</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/cos-tracker/toggle-realised/{id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>COS Tracker</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>/cos</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/tracker-monthly</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/tracker-monthly when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>COS Tracker</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>/cos</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>`button-close-drawer` button</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>'Close drawer' button — triggers the 'close drawer' action on the COS Tracker screen.</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>COS Tracker</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>/cos</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>`input-search-detail` input</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'search detail'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>COS Tracker</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>/cos</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>`select-project-filter` selector</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'project filter'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>COS Tracker</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>/cos</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>`select-state-filter` selector</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'state filter'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>GP Tracker</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>/gp-tracker</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/gp-tracker</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>On load, the GP Tracker screen calls /api/gp-tracker to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the GP Tracker page.</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>GP Tracker</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>/gp-tracker</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/gp-tracker/month-detail?monthKey={encodeURIComponent(monthKey)}</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>On load, the GP Tracker screen calls /api/gp-tracker/month-detail?monthKey={encodeURIComponent(monthKey)} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the GP Tracker page.</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>GP Tracker</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>/gp-tracker</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>`button-close-month-detail` button</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>'Close month detail' button — triggers the 'close month detail' action on the GP Tracker screen.</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>GP Tracker</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>/gp-tracker</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>`button-toggle-monthly` button</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>'Toggle monthly' button — triggers the 'toggle monthly' action on the GP Tracker screen.</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>GP Tracker</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>/gp-tracker</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>`button-toggle-projects` button</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>'Toggle projects' button — triggers the 'toggle projects' action on the GP Tracker screen.</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>GP Tracker</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>/gp-tracker</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>`button-toggle-ytd` button</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>'Toggle ytd' button — triggers the 'toggle ytd' action on the GP Tracker screen.</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>GP Tracker</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>/gp-tracker</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>`input-search-projects` input</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'search projects'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /api/fye-revenue-tracking/lost-deals/{id}</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>Sends a DELETE to /api/fye-revenue-tracking/lost-deals/{id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /api/fye-revenue-tracking/pipeline/{id}</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>Sends a DELETE to /api/fye-revenue-tracking/pipeline/{id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/fye-revenue-tracking/budgets</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>On load, the FYE Revenue Tracking screen calls /api/fye-revenue-tracking/budgets to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the FYE Revenue Tracking page.</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/fye-revenue-tracking/dashboard</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>On load, the FYE Revenue Tracking screen calls /api/fye-revenue-tracking/dashboard to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the FYE Revenue Tracking page.</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/fye-revenue-tracking/detail</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>On load, the FYE Revenue Tracking screen calls /api/fye-revenue-tracking/detail to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the FYE Revenue Tracking page.</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/fye-revenue-tracking/kpis</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>On load, the FYE Revenue Tracking screen calls /api/fye-revenue-tracking/kpis to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the FYE Revenue Tracking page.</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/fye-revenue-tracking/lost-deals</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>On load, the FYE Revenue Tracking screen calls /api/fye-revenue-tracking/lost-deals to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the FYE Revenue Tracking page.</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/fye-revenue-tracking/pipeline</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>On load, the FYE Revenue Tracking screen calls /api/fye-revenue-tracking/pipeline to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the FYE Revenue Tracking page.</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/fye-revenue-tracking/snapshots</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>On load, the FYE Revenue Tracking screen calls /api/fye-revenue-tracking/snapshots to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the FYE Revenue Tracking page.</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/fye-revenue-tracking/years</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>On load, the FYE Revenue Tracking screen calls /api/fye-revenue-tracking/years to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the FYE Revenue Tracking page.</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/fye-revenue-tracking/budgets</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/fye-revenue-tracking/budgets when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H454" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/fye-revenue-tracking/lost-deals</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/fye-revenue-tracking/lost-deals when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H455" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/fye-revenue-tracking/pipeline</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/fye-revenue-tracking/pipeline when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H456" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/fye-revenue-tracking/snapshots</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/fye-revenue-tracking/snapshots when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H457" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>PUT /api/fye-revenue-tracking/detail/inline-edit</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PUT to /api/fye-revenue-tracking/detail/inline-edit when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H458" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>PUT /api/fye-revenue-tracking/lost-deals/{data.id}</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PUT to /api/fye-revenue-tracking/lost-deals/{data.id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H459" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>PUT /api/fye-revenue-tracking/pipeline/{data.id}</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PUT to /api/fye-revenue-tracking/pipeline/{data.id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>PUT /api/fye-revenue-tracking/snapshots/{id}/approve</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PUT to /api/fye-revenue-tracking/snapshots/{id}/approve when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>FYE Revenue Tracking</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>/fye-revenue-tracking</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>PUT /api/fye-revenue-tracking/snapshots/{id}/submit</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PUT to /api/fye-revenue-tracking/snapshots/{id}/submit when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>Financial Linking</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName/financial-linking</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>`button-back-to-project` button</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>'Back to project' button — triggers the 'back to project' action on the Financial Linking screen.</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>Financial Linking</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName/financial-linking</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>`button-bulk-link` button</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>'Bulk link' button — triggers the 'bulk link' action on the Financial Linking screen.</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>Financial Linking</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName/financial-linking</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>`button-toggle-expenses` button</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>'Toggle expenses' button — triggers the 'toggle expenses' action on the Financial Linking screen.</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>Financial Linking</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName/financial-linking</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>`button-toggle-insights` button</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>'Toggle insights' button — triggers the 'toggle insights' action on the Financial Linking screen.</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>Financial Linking</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName/financial-linking</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>`button-toggle-revenue` button</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>'Toggle revenue' button — triggers the 'toggle revenue' action on the Financial Linking screen.</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>Financial Linking</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName/financial-linking</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>`select-bulk-category` selector</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'bulk category'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>Financial Linking</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>/project/:projectName/financial-linking</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>`select-bulk-task` selector</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'bulk task'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>Financial Review Queue</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>/governance/financial-reviews</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/financial-reviews/pending</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Financial Review Queue screen calls /api/financial-reviews/pending to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Financial Review Queue page.</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/counterparties</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Invoice Patterns screen calls /api/counterparties to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Invoice Patterns page.</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/counterparties/{editingId}</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Invoice Patterns screen calls /api/counterparties/{editingId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Invoice Patterns page.</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/counterparties/{id}</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Invoice Patterns screen calls /api/counterparties/{id} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Invoice Patterns page.</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Invoice Patterns screen calls /api/invoice-patterns to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Invoice Patterns page.</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/invoice-patterns/{editingId}</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Invoice Patterns screen calls /api/invoice-patterns/{editingId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Invoice Patterns page.</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/invoice-patterns/{id}</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Invoice Patterns screen calls /api/invoice-patterns/{id} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Invoice Patterns page.</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/procurement-analysis/classify</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Invoice Patterns screen calls /api/procurement-analysis/classify to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Invoice Patterns page.</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/procurement-analysis/pattern-stats</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Invoice Patterns screen calls /api/procurement-analysis/pattern-stats to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Invoice Patterns page.</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/summary</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Invoice Patterns screen calls /api/subcontractor-dashboard/summary to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Invoice Patterns page.</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>`input-confidence-weight` input</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'confidence weight'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>`input-counterparty-name` input</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'counterparty name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>`input-cp-alias` input</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'cp alias'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H482" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>`input-cp-name` input</t>
+        </is>
+      </c>
+      <c r="D483" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'cp name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F483" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H483" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>`input-example` input</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'example'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>`input-pattern-value` input</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'pattern value'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F485" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>`input-search-counterparties` input</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'search counterparties'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>`input-search-patterns` input</t>
+        </is>
+      </c>
+      <c r="D487" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'search patterns'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F487" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G487" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H487" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>`select-cp-type` selector</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'cp type'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H488" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>`select-inferred-type` selector</t>
+        </is>
+      </c>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'inferred type'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F489" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G489" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>`select-pattern-type` selector</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'pattern type'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>`tab-counterparties` tab</t>
+        </is>
+      </c>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Invoice Patterns view to the 'counterparties' tab.</t>
+        </is>
+      </c>
+      <c r="F491" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H491" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Patterns</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>`tab-patterns` tab</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Invoice Patterns view to the 'patterns' tab.</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>PO Approval Board</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>/po-approval-board</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/po/board/all</t>
+        </is>
+      </c>
+      <c r="D493" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PO Approval Board screen calls /api/po/board/all to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F493" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PO Approval Board page.</t>
+        </is>
+      </c>
+      <c r="H493" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>PO Approval Board</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>/po-approval-board</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/po/board/my-reviews</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>On load, the PO Approval Board screen calls /api/po/board/my-reviews to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the PO Approval Board page.</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>PO Approval Board</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <t>/po-approval-board</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/po/{po.id}/review</t>
+        </is>
+      </c>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/po/{po.id}/review when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F495" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G495" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H495" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>PO Approval Board</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>/po-approval-board</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/po/{po.id}/submit</t>
+        </is>
+      </c>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/po/{po.id}/submit when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F496" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H496" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>Payment Request Board</t>
+        </is>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>/payment-request-board</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/payment-requests/board</t>
+        </is>
+      </c>
+      <c r="D497" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E497" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Payment Request Board screen calls /api/payment-requests/board to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F497" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G497" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Payment Request Board page.</t>
+        </is>
+      </c>
+      <c r="H497" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>Payment Request Board</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>/payment-request-board</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/payment-requests/{pr.id}/status</t>
+        </is>
+      </c>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/payment-requests/{pr.id}/status when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F498" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G498" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H498" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>Payment Request Board</t>
+        </is>
+      </c>
+      <c r="B499" s="2" t="inlineStr">
+        <is>
+          <t>/payment-request-board</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/payment-requests/{pr.id}/review</t>
+        </is>
+      </c>
+      <c r="D499" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E499" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/payment-requests/{pr.id}/review when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F499" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G499" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H499" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>Payment Batch Manager</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>/payment-batch-manager</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/payment-batches</t>
+        </is>
+      </c>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Payment Batch Manager screen calls /api/payment-batches to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F500" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G500" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Payment Batch Manager page.</t>
+        </is>
+      </c>
+      <c r="H500" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>Payment Batch Manager</t>
+        </is>
+      </c>
+      <c r="B501" s="2" t="inlineStr">
+        <is>
+          <t>/payment-batch-manager</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/payment-batches/{batch.id}/approve</t>
+        </is>
+      </c>
+      <c r="D501" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/payment-batches/{batch.id}/approve when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F501" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G501" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H501" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>Payment Batch Manager</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>/payment-batch-manager</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/payment-batches/{batch.id}/confirm</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/payment-batches/{batch.id}/confirm when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F502" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H502" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>Payment Batch Manager</t>
+        </is>
+      </c>
+      <c r="B503" s="2" t="inlineStr">
+        <is>
+          <t>/payment-batch-manager</t>
+        </is>
+      </c>
+      <c r="C503" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/payment-batches/{batch.id}/release</t>
+        </is>
+      </c>
+      <c r="D503" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/payment-batches/{batch.id}/release when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F503" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G503" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H503" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>Payment Batch Manager</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>/payment-batch-manager</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/payment-batches/{batch.id}/submit</t>
+        </is>
+      </c>
+      <c r="D504" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/payment-batches/{batch.id}/submit when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G504" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H504" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C505" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/invoice-patterns</t>
+        </is>
+      </c>
+      <c r="D505" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Subcontractor Dashboard screen calls /api/invoice-patterns to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F505" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G505" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Subcontractor Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H505" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/procurement-analysis/pattern-stats</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Subcontractor Dashboard screen calls /api/procurement-analysis/pattern-stats to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G506" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Subcontractor Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H506" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C507" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/counterparty/{encodeURIComponent(name)}</t>
+        </is>
+      </c>
+      <c r="D507" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Subcontractor Dashboard screen calls /api/subcontractor-dashboard/counterparty/{encodeURIComponent(name)} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F507" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G507" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Subcontractor Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H507" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/counterparty/{encodeURIComponent(selectedCp)}</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Subcontractor Dashboard screen calls /api/subcontractor-dashboard/counterparty/{encodeURIComponent(selectedCp)} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Subcontractor Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C509" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/counterparty/{encodeURIComponent(selectedCp)}/type</t>
+        </is>
+      </c>
+      <c r="D509" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Subcontractor Dashboard screen calls /api/subcontractor-dashboard/counterparty/{encodeURIComponent(selectedCp)}/type to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F509" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G509" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Subcontractor Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H509" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/detail</t>
+        </is>
+      </c>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Subcontractor Dashboard screen calls /api/subcontractor-dashboard/detail to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F510" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G510" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Subcontractor Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H510" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B511" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C511" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/detail/{encodeURIComponent(selectedCp)}</t>
+        </is>
+      </c>
+      <c r="D511" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Subcontractor Dashboard screen calls /api/subcontractor-dashboard/detail/{encodeURIComponent(selectedCp)} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F511" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G511" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Subcontractor Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H511" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/link-counterparty</t>
+        </is>
+      </c>
+      <c r="D512" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Subcontractor Dashboard screen calls /api/subcontractor-dashboard/link-counterparty to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F512" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G512" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Subcontractor Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H512" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/merge</t>
+        </is>
+      </c>
+      <c r="D513" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Subcontractor Dashboard screen calls /api/subcontractor-dashboard/merge to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F513" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G513" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Subcontractor Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H513" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/overdue</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Subcontractor Dashboard screen calls /api/subcontractor-dashboard/overdue to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G514" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Subcontractor Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H514" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B515" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C515" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/rename</t>
+        </is>
+      </c>
+      <c r="D515" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Subcontractor Dashboard screen calls /api/subcontractor-dashboard/rename to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F515" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G515" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Subcontractor Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H515" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/summary</t>
+        </is>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Subcontractor Dashboard screen calls /api/subcontractor-dashboard/summary to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G516" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Subcontractor Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H516" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B517" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C517" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/summary?{params}</t>
+        </is>
+      </c>
+      <c r="D517" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Subcontractor Dashboard screen calls /api/subcontractor-dashboard/summary?{params} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F517" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G517" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Subcontractor Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H517" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/subcontractor-dashboard/supplier-details/{encodeURIComponent(counterpartyName)}</t>
+        </is>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Subcontractor Dashboard screen calls /api/subcontractor-dashboard/supplier-details/{encodeURIComponent(counterpartyName)} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G518" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Subcontractor Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H518" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C519" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-counterparty` input</t>
+        </is>
+      </c>
+      <c r="D519" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E519" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new counterparty'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F519" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G519" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H519" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>`input-rename-counterparty` input</t>
+        </is>
+      </c>
+      <c r="D520" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'rename counterparty'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F520" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G520" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H520" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B521" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C521" s="2" t="inlineStr">
+        <is>
+          <t>`input-search` input</t>
+        </is>
+      </c>
+      <c r="D521" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E521" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F521" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G521" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H521" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>`input-supplier-account` input</t>
+        </is>
+      </c>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'supplier account'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F522" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G522" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H522" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B523" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C523" s="2" t="inlineStr">
+        <is>
+          <t>`input-supplier-address` input</t>
+        </is>
+      </c>
+      <c r="D523" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'supplier address'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F523" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G523" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H523" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>`input-supplier-bank` input</t>
+        </is>
+      </c>
+      <c r="D524" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'supplier bank'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F524" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G524" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H524" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B525" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C525" s="2" t="inlineStr">
+        <is>
+          <t>`input-supplier-branch` input</t>
+        </is>
+      </c>
+      <c r="D525" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'supplier branch'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F525" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G525" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H525" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>`input-supplier-contact-person` input</t>
+        </is>
+      </c>
+      <c r="D526" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'supplier contact person'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F526" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G526" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H526" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B527" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>`input-supplier-email` input</t>
+        </is>
+      </c>
+      <c r="D527" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'supplier email'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F527" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G527" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H527" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>`input-supplier-notes` input</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'supplier notes'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F528" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G528" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H528" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B529" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C529" s="2" t="inlineStr">
+        <is>
+          <t>`input-supplier-payment-terms` input</t>
+        </is>
+      </c>
+      <c r="D529" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E529" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'supplier payment terms'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F529" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G529" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H529" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>`input-supplier-phone` input</t>
+        </is>
+      </c>
+      <c r="D530" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'supplier phone'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F530" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G530" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H530" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B531" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C531" s="2" t="inlineStr">
+        <is>
+          <t>`input-supplier-reg` input</t>
+        </is>
+      </c>
+      <c r="D531" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E531" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'supplier reg'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F531" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G531" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H531" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>`input-supplier-vat` input</t>
+        </is>
+      </c>
+      <c r="D532" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'supplier vat'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F532" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G532" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H532" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B533" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C533" s="2" t="inlineStr">
+        <is>
+          <t>`link-panel` link</t>
+        </is>
+      </c>
+      <c r="D533" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="inlineStr">
+        <is>
+          <t>Navigates to the 'panel' destination.</t>
+        </is>
+      </c>
+      <c r="F533" s="2" t="inlineStr">
+        <is>
+          <t>Nothing on click.</t>
+        </is>
+      </c>
+      <c r="G533" s="2" t="inlineStr">
+        <is>
+          <t>Varies — see source.</t>
+        </is>
+      </c>
+      <c r="H533" s="2" t="inlineStr">
+        <is>
+          <t>None on click.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>`select-cp-type` selector</t>
+        </is>
+      </c>
+      <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'cp type'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F534" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G534" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H534" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C535" s="2" t="inlineStr">
+        <is>
+          <t>`select-link-target` selector</t>
+        </is>
+      </c>
+      <c r="D535" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'link target'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F535" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G535" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H535" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>`select-merge-target` selector</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'merge target'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F536" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G536" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H536" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>`select-new-cp-type` selector</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'new cp type'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F537" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G537" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H537" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>`select-project-filter` selector</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'project filter'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G538" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H538" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>`select-type-filter` selector</t>
+        </is>
+      </c>
+      <c r="D539" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'type filter'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F539" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G539" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H539" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>`tab-all-invoices` tab</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Subcontractor Dashboard view to the 'all invoices' tab.</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H540" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>`tab-invoiced` tab</t>
+        </is>
+      </c>
+      <c r="D541" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Subcontractor Dashboard view to the 'invoiced' tab.</t>
+        </is>
+      </c>
+      <c r="F541" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G541" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H541" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>`tab-outstanding-invoices` tab</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Subcontractor Dashboard view to the 'outstanding invoices' tab.</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G542" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H542" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>`tab-paid-invoices` tab</t>
+        </is>
+      </c>
+      <c r="D543" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Subcontractor Dashboard view to the 'paid invoices' tab.</t>
+        </is>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G543" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H543" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>Subcontractor Dashboard</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>/subcontractor-dashboard</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>`tab-planned` tab</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Subcontractor Dashboard view to the 'planned' tab.</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G544" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H544" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Dashboard</t>
+        </is>
+      </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <t>/procurement</t>
+        </is>
+      </c>
+      <c r="C545" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/procurement-items</t>
+        </is>
+      </c>
+      <c r="D545" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Procurement Dashboard screen calls /api/procurement-items to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F545" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G545" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Procurement Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H545" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Dashboard</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>/procurement</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/procurement-items-all</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Procurement Dashboard screen calls /api/procurement-items-all to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G546" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Procurement Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H546" s="2" t="inlineStr">
         <is>
           <t>See Data Sources sheet for the handler + tables.</t>
         </is>

--- a/docs/workbook/emergent-energy-system-map.xlsx
+++ b/docs/workbook/emergent-energy-system-map.xlsx
@@ -5722,7 +5722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H546"/>
+  <dimension ref="A1:H558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -28662,6 +28662,510 @@
         </is>
       </c>
       <c r="H546" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>QM Dashboard (Quality)</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>/quality</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>`input-qm-project-search` input</t>
+        </is>
+      </c>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'qm project search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F547" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G547" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H547" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>QM Dashboard (Quality)</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>/quality</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>`input-qm-search` input</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'qm search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G548" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H548" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>QM Dashboard (Quality)</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>/quality</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>`input-warning-reason` input</t>
+        </is>
+      </c>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'warning reason'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F549" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G549" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H549" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>QM Dashboard (Quality)</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>/quality</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>`select-qm-project` selector</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'qm project'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G550" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>QM Dashboard (Quality)</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>/quality</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>`select-status-filter` selector</t>
+        </is>
+      </c>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'status filter'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F551" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G551" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H551" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>HSE Dashboard</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>/hse</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/hse/corrective-actions</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>On load, the HSE Dashboard screen calls /api/hse/corrective-actions to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G552" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the HSE Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H552" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>HSE Dashboard</t>
+        </is>
+      </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <t>/hse</t>
+        </is>
+      </c>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/hse/incidents</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="inlineStr">
+        <is>
+          <t>On load, the HSE Dashboard screen calls /api/hse/incidents to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F553" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G553" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the HSE Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H553" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>HSE Dashboard</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>/hse</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/hse/incidents/{id}</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/hse/incidents/{id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G554" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H554" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>HSE Dashboard</t>
+        </is>
+      </c>
+      <c r="B555" s="2" t="inlineStr">
+        <is>
+          <t>/hse</t>
+        </is>
+      </c>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/hse/incidents</t>
+        </is>
+      </c>
+      <c r="D555" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/hse/incidents when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F555" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G555" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H555" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>Commissioning Dashboard</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>/commissioning-dashboard</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/commissioning-dashboard/{projectId}</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Commissioning Dashboard screen calls /api/commissioning-dashboard/{projectId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G556" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Commissioning Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H556" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>Commissioning Dashboard</t>
+        </is>
+      </c>
+      <c r="B557" s="2" t="inlineStr">
+        <is>
+          <t>/commissioning-dashboard</t>
+        </is>
+      </c>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/commissioning-dashboard/{projectId}/refresh</t>
+        </is>
+      </c>
+      <c r="D557" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Commissioning Dashboard screen calls /api/commissioning-dashboard/{projectId}/refresh to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F557" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G557" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Commissioning Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H557" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>Commissioning Dashboard</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>/commissioning-dashboard</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/commissioning-dashboard/{projectId}/upload</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Commissioning Dashboard screen calls /api/commissioning-dashboard/{projectId}/upload to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G558" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Commissioning Dashboard page.</t>
+        </is>
+      </c>
+      <c r="H558" s="2" t="inlineStr">
         <is>
           <t>See Data Sources sheet for the handler + tables.</t>
         </is>

--- a/docs/workbook/emergent-energy-system-map.xlsx
+++ b/docs/workbook/emergent-energy-system-map.xlsx
@@ -5722,7 +5722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H558"/>
+  <dimension ref="A1:H737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -29166,6 +29166,7524 @@
         </is>
       </c>
       <c r="H558" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="inlineStr">
+        <is>
+          <t>Admin Approvals</t>
+        </is>
+      </c>
+      <c r="B559" s="2" t="inlineStr">
+        <is>
+          <t>/admin/approvals</t>
+        </is>
+      </c>
+      <c r="C559" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/approvals/general/{approvalId}</t>
+        </is>
+      </c>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Approvals screen calls /api/approvals/general/{approvalId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F559" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G559" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Approvals page.</t>
+        </is>
+      </c>
+      <c r="H559" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>Admin Approvals</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>/admin/approvals</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/approvals/pending</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Approvals screen calls /api/approvals/pending to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G560" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Approvals page.</t>
+        </is>
+      </c>
+      <c r="H560" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="inlineStr">
+        <is>
+          <t>Admin Approvals</t>
+        </is>
+      </c>
+      <c r="B561" s="2" t="inlineStr">
+        <is>
+          <t>/admin/approvals</t>
+        </is>
+      </c>
+      <c r="C561" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/deliverables/{deliverableId}</t>
+        </is>
+      </c>
+      <c r="D561" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E561" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Approvals screen calls /api/deliverables/{deliverableId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F561" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G561" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Approvals page.</t>
+        </is>
+      </c>
+      <c r="H561" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>Admin Approvals</t>
+        </is>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>/admin/approvals</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/deliverables/{deliverableId}/feedback</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Approvals screen calls /api/deliverables/{deliverableId}/feedback to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F562" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G562" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Approvals page.</t>
+        </is>
+      </c>
+      <c r="H562" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>Admin Approvals</t>
+        </is>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
+        <is>
+          <t>/admin/approvals</t>
+        </is>
+      </c>
+      <c r="C563" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/eng-stages/approvals/{approvalId}</t>
+        </is>
+      </c>
+      <c r="D563" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Approvals screen calls /api/eng-stages/approvals/{approvalId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F563" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G563" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Approvals page.</t>
+        </is>
+      </c>
+      <c r="H563" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>Admin Approvals</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>/admin/approvals</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/quality/project/{encodeURIComponent(item.projectName)}/item/{itemInstanceId}/approve</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Approvals screen calls /api/quality/project/{encodeURIComponent(item.projectName)}/item/{itemInstanceId}/approve to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G564" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Approvals page.</t>
+        </is>
+      </c>
+      <c r="H564" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>Admin Approvals</t>
+        </is>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>/admin/approvals</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>`button-clear-filter` button</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="inlineStr">
+        <is>
+          <t>'Clear filter' button — triggers the 'clear filter' action on the Admin Approvals screen.</t>
+        </is>
+      </c>
+      <c r="F565" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G565" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H565" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>Admin Approvals</t>
+        </is>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>/admin/approvals</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="inlineStr">
+        <is>
+          <t>`input-reason` input</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'reason'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F566" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G566" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H566" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="inlineStr">
+        <is>
+          <t>Admin Backfill</t>
+        </is>
+      </c>
+      <c r="B567" s="2" t="inlineStr">
+        <is>
+          <t>/admin/data-migration-status</t>
+        </is>
+      </c>
+      <c r="C567" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/backfill/status</t>
+        </is>
+      </c>
+      <c r="D567" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E567" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Backfill screen calls /api/admin/backfill/status to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F567" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G567" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Backfill page.</t>
+        </is>
+      </c>
+      <c r="H567" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>Admin Backfill</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>/admin/data-migration-status</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/admin/backfill/opportunities-from-pd-tickets</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/admin/backfill/opportunities-from-pd-tickets when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F568" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G568" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H568" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>Admin Backfill</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>/admin/data-migration-status</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/admin/backfill/sites-from-projects</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/admin/backfill/sites-from-projects when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F569" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G569" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H569" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>Admin Pipedrive</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>/admin/pipedrive</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/pipedrive/status</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Pipedrive screen calls /api/admin/pipedrive/status to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F570" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G570" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Pipedrive page.</t>
+        </is>
+      </c>
+      <c r="H570" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="inlineStr">
+        <is>
+          <t>Admin Pipedrive</t>
+        </is>
+      </c>
+      <c r="B571" s="2" t="inlineStr">
+        <is>
+          <t>/admin/pipedrive</t>
+        </is>
+      </c>
+      <c r="C571" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/pipedrive/sync-log</t>
+        </is>
+      </c>
+      <c r="D571" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E571" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Pipedrive screen calls /api/admin/pipedrive/sync-log to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F571" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G571" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Pipedrive page.</t>
+        </is>
+      </c>
+      <c r="H571" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>Admin Pipedrive</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>/admin/pipedrive</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/opportunities</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Pipedrive screen calls /api/opportunities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F572" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G572" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Pipedrive page.</t>
+        </is>
+      </c>
+      <c r="H572" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>Admin Pipedrive</t>
+        </is>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>/admin/pipedrive</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/admin/pipedrive/sync</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E573" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/admin/pipedrive/sync when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F573" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G573" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H573" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-project-edit` button</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm project edit' button — triggers the 'confirm project edit' action on the Admin Recovery screen.</t>
+        </is>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G574" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H574" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B575" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C575" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-restore` button</t>
+        </is>
+      </c>
+      <c r="D575" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E575" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm restore' button — triggers the 'confirm restore' action on the Admin Recovery screen.</t>
+        </is>
+      </c>
+      <c r="F575" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G575" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H575" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-task-edit` button</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm task edit' button — triggers the 'confirm task edit' action on the Admin Recovery screen.</t>
+        </is>
+      </c>
+      <c r="F576" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G576" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H576" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="inlineStr">
+        <is>
+          <t>`button-filter-all-types` button</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="inlineStr">
+        <is>
+          <t>'Filter all types' button — triggers the 'filter all types' action on the Admin Recovery screen.</t>
+        </is>
+      </c>
+      <c r="F577" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G577" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H577" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>`button-restore-selected` button</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>'Restore selected' button — triggers the 'restore selected' action on the Admin Recovery screen.</t>
+        </is>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G578" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H578" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="inlineStr">
+        <is>
+          <t>`button-save-project-edit` button</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="inlineStr">
+        <is>
+          <t>'Save project edit' button — triggers the 'save project edit' action on the Admin Recovery screen.</t>
+        </is>
+      </c>
+      <c r="F579" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G579" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H579" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>`button-save-task-edit` button</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr">
+        <is>
+          <t>'Save task edit' button — triggers the 'save task edit' action on the Admin Recovery screen.</t>
+        </is>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G580" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H580" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="inlineStr">
+        <is>
+          <t>`input-deleted-search` input</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'deleted search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F581" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G581" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H581" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-project-client-id` input</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit project client id'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G582" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-project-contract-value` input</t>
+        </is>
+      </c>
+      <c r="D583" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit project contract value'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F583" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G583" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H583" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-project-exec-phase` input</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit project exec phase'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F584" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G584" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H584" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-project-name` input</t>
+        </is>
+      </c>
+      <c r="D585" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit project name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F585" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G585" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H585" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-project-pd` input</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit project pd'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F586" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G586" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H586" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-project-phase` input</t>
+        </is>
+      </c>
+      <c r="D587" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit project phase'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F587" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G587" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H587" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-project-pm` input</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit project pm'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F588" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G588" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H588" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B589" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-project-rag-comment` input</t>
+        </is>
+      </c>
+      <c r="D589" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit project rag comment'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F589" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G589" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H589" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B590" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-project-size-kwp` input</t>
+        </is>
+      </c>
+      <c r="D590" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit project size kwp'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F590" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G590" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H590" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-task-due-date` input</t>
+        </is>
+      </c>
+      <c r="D591" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E591" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit task due date'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F591" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G591" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H591" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-task-priority` input</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit task priority'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F592" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G592" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H592" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B593" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-task-status` input</t>
+        </is>
+      </c>
+      <c r="D593" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E593" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit task status'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F593" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G593" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H593" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-task-title` input</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit task title'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F594" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G594" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H594" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B595" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C595" s="2" t="inlineStr">
+        <is>
+          <t>`input-recovery-project-search` input</t>
+        </is>
+      </c>
+      <c r="D595" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E595" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'recovery project search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F595" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G595" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H595" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>`input-recovery-task-search` input</t>
+        </is>
+      </c>
+      <c r="D596" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'recovery task search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F596" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G596" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H596" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B597" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>`select-edit-project-rag` selector</t>
+        </is>
+      </c>
+      <c r="D597" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E597" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'edit project rag'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F597" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G597" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H597" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>`select-edit-task-owner` selector</t>
+        </is>
+      </c>
+      <c r="D598" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'edit task owner'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F598" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G598" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H598" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B599" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C599" s="2" t="inlineStr">
+        <is>
+          <t>`select-edit-task-project` selector</t>
+        </is>
+      </c>
+      <c r="D599" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E599" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'edit task project'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F599" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G599" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H599" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>`select-recovery-task-type` selector</t>
+        </is>
+      </c>
+      <c r="D600" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'recovery task type'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F600" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G600" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H600" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>`tab-recovery-deleted` tab</t>
+        </is>
+      </c>
+      <c r="D601" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Admin Recovery view to the 'recovery deleted' tab.</t>
+        </is>
+      </c>
+      <c r="F601" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G601" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H601" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>`tab-recovery-imports` tab</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Admin Recovery view to the 'recovery imports' tab.</t>
+        </is>
+      </c>
+      <c r="F602" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G602" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H602" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B603" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>`tab-recovery-projects` tab</t>
+        </is>
+      </c>
+      <c r="D603" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E603" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Admin Recovery view to the 'recovery projects' tab.</t>
+        </is>
+      </c>
+      <c r="F603" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G603" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H603" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>Admin Recovery</t>
+        </is>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>/admin/recovery</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>`tab-recovery-tasks` tab</t>
+        </is>
+      </c>
+      <c r="D604" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Admin Recovery view to the 'recovery tasks' tab.</t>
+        </is>
+      </c>
+      <c r="F604" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G604" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H604" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B605" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C605" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/pd-visibility</t>
+        </is>
+      </c>
+      <c r="D605" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E605" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/pd-visibility to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F605" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G605" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H605" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B606" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C606" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/pd-visibility/{configId}</t>
+        </is>
+      </c>
+      <c r="D606" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/pd-visibility/{configId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F606" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G606" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H606" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B607" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C607" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/pd-visibility/role</t>
+        </is>
+      </c>
+      <c r="D607" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E607" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/pd-visibility/role to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F607" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G607" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H607" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B608" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C608" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/pd-visibility/user</t>
+        </is>
+      </c>
+      <c r="D608" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E608" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/pd-visibility/user to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F608" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G608" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H608" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B609" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C609" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/permission-audit-log?{params}</t>
+        </is>
+      </c>
+      <c r="D609" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E609" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/permission-audit-log?{params} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F609" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G609" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H609" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B610" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C610" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/user-overrides</t>
+        </is>
+      </c>
+      <c r="D610" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/user-overrides to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F610" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G610" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H610" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B611" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C611" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/user-overrides/{overrideId}</t>
+        </is>
+      </c>
+      <c r="D611" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E611" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/user-overrides/{overrideId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F611" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G611" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H611" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/user-overrides/{userId}</t>
+        </is>
+      </c>
+      <c r="D612" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/user-overrides/{userId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F612" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G612" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H612" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B613" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C613" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/users</t>
+        </is>
+      </c>
+      <c r="D613" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E613" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/users to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F613" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G613" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H613" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C614" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/users/{id}/department</t>
+        </is>
+      </c>
+      <c r="D614" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/users/{id}/department to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F614" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G614" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H614" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B615" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C615" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/users/{id}/role</t>
+        </is>
+      </c>
+      <c r="D615" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E615" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/users/{id}/role to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F615" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G615" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H615" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B616" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C616" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/users/{showPasswordDialog.id}/password</t>
+        </is>
+      </c>
+      <c r="D616" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/users/{showPasswordDialog.id}/password to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F616" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G616" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H616" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B617" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C617" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/users/{user.id}</t>
+        </is>
+      </c>
+      <c r="D617" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E617" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/users/{user.id} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F617" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G617" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H617" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C618" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/workstream-visibility</t>
+        </is>
+      </c>
+      <c r="D618" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E618" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/workstream-visibility to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F618" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G618" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H618" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B619" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C619" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/workstream-visibility/{configId}</t>
+        </is>
+      </c>
+      <c r="D619" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E619" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/workstream-visibility/{configId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F619" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G619" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H619" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C620" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/workstream-visibility/role</t>
+        </is>
+      </c>
+      <c r="D620" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/admin/workstream-visibility/role to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F620" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G620" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H620" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B621" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C621" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/auth/permissions</t>
+        </is>
+      </c>
+      <c r="D621" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/auth/permissions to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F621" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G621" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H621" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/roles</t>
+        </is>
+      </c>
+      <c r="D622" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/roles to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F622" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G622" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H622" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B623" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C623" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/roles/{selected.role}</t>
+        </is>
+      </c>
+      <c r="D623" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/roles/{selected.role} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F623" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G623" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H623" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B624" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C624" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/roles/{selected.role}/archive</t>
+        </is>
+      </c>
+      <c r="D624" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/roles/{selected.role}/archive to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F624" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G624" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H624" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B625" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C625" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/roles/{selected.role}/clone</t>
+        </is>
+      </c>
+      <c r="D625" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E625" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/roles/{selected.role}/clone to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F625" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G625" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H625" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B626" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C626" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/roles/control-center</t>
+        </is>
+      </c>
+      <c r="D626" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E626" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Admin Roles screen calls /api/roles/control-center to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F626" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G626" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Admin Roles page.</t>
+        </is>
+      </c>
+      <c r="H626" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B627" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C627" s="2" t="inlineStr">
+        <is>
+          <t>`button-add-user` button</t>
+        </is>
+      </c>
+      <c r="D627" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E627" s="2" t="inlineStr">
+        <is>
+          <t>'Add user' button — triggers the 'add user' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F627" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G627" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H627" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B628" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C628" s="2" t="inlineStr">
+        <is>
+          <t>`button-archive-role` button</t>
+        </is>
+      </c>
+      <c r="D628" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E628" s="2" t="inlineStr">
+        <is>
+          <t>'Archive role' button — triggers the 'archive role' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F628" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G628" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H628" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B629" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C629" s="2" t="inlineStr">
+        <is>
+          <t>`button-cancel-create` button</t>
+        </is>
+      </c>
+      <c r="D629" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E629" s="2" t="inlineStr">
+        <is>
+          <t>'Cancel create' button — triggers the 'cancel create' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F629" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G629" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H629" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B630" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C630" s="2" t="inlineStr">
+        <is>
+          <t>`button-cancel-create-user` button</t>
+        </is>
+      </c>
+      <c r="D630" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E630" s="2" t="inlineStr">
+        <is>
+          <t>'Cancel create user' button — triggers the 'cancel create user' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F630" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G630" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H630" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B631" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C631" s="2" t="inlineStr">
+        <is>
+          <t>`button-cancel-delete` button</t>
+        </is>
+      </c>
+      <c r="D631" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E631" s="2" t="inlineStr">
+        <is>
+          <t>'Cancel delete' button — triggers the 'cancel delete' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F631" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G631" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H631" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B632" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C632" s="2" t="inlineStr">
+        <is>
+          <t>`button-cancel-password` button</t>
+        </is>
+      </c>
+      <c r="D632" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="inlineStr">
+        <is>
+          <t>'Cancel password' button — triggers the 'cancel password' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F632" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G632" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H632" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B633" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C633" s="2" t="inlineStr">
+        <is>
+          <t>`button-clone-role` button</t>
+        </is>
+      </c>
+      <c r="D633" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E633" s="2" t="inlineStr">
+        <is>
+          <t>'Clone role' button — triggers the 'clone role' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F633" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G633" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H633" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B634" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C634" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-archive` button</t>
+        </is>
+      </c>
+      <c r="D634" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E634" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm archive' button — triggers the 'confirm archive' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F634" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G634" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H634" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B635" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C635" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-clone` button</t>
+        </is>
+      </c>
+      <c r="D635" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E635" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm clone' button — triggers the 'confirm clone' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F635" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G635" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H635" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B636" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C636" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-create` button</t>
+        </is>
+      </c>
+      <c r="D636" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E636" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm create' button — triggers the 'confirm create' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F636" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G636" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H636" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B637" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C637" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-create-user` button</t>
+        </is>
+      </c>
+      <c r="D637" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E637" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm create user' button — triggers the 'confirm create user' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F637" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G637" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H637" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B638" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C638" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-delete` button</t>
+        </is>
+      </c>
+      <c r="D638" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E638" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm delete' button — triggers the 'confirm delete' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F638" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G638" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H638" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B639" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C639" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-delete-role` button</t>
+        </is>
+      </c>
+      <c r="D639" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E639" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm delete role' button — triggers the 'confirm delete role' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F639" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G639" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H639" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C640" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-password` button</t>
+        </is>
+      </c>
+      <c r="D640" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E640" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm password' button — triggers the 'confirm password' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F640" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G640" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H640" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B641" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C641" s="2" t="inlineStr">
+        <is>
+          <t>`button-create-role` button</t>
+        </is>
+      </c>
+      <c r="D641" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E641" s="2" t="inlineStr">
+        <is>
+          <t>'Create role' button — triggers the 'create role' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F641" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G641" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H641" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B642" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C642" s="2" t="inlineStr">
+        <is>
+          <t>`button-delete-role` button</t>
+        </is>
+      </c>
+      <c r="D642" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E642" s="2" t="inlineStr">
+        <is>
+          <t>'Delete role' button — triggers the 'delete role' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F642" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G642" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H642" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B643" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C643" s="2" t="inlineStr">
+        <is>
+          <t>`button-grant-all-global` button</t>
+        </is>
+      </c>
+      <c r="D643" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E643" s="2" t="inlineStr">
+        <is>
+          <t>'Grant all global' button — triggers the 'grant all global' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F643" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G643" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H643" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B644" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C644" s="2" t="inlineStr">
+        <is>
+          <t>`button-reset-changes` button</t>
+        </is>
+      </c>
+      <c r="D644" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E644" s="2" t="inlineStr">
+        <is>
+          <t>'Reset changes' button — triggers the 'reset changes' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F644" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G644" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H644" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B645" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C645" s="2" t="inlineStr">
+        <is>
+          <t>`button-revoke-all-global` button</t>
+        </is>
+      </c>
+      <c r="D645" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E645" s="2" t="inlineStr">
+        <is>
+          <t>'Revoke all global' button — triggers the 'revoke all global' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F645" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G645" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H645" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B646" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C646" s="2" t="inlineStr">
+        <is>
+          <t>`button-save-changes` button</t>
+        </is>
+      </c>
+      <c r="D646" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E646" s="2" t="inlineStr">
+        <is>
+          <t>'Save changes' button — triggers the 'save changes' action on the Admin Roles screen.</t>
+        </is>
+      </c>
+      <c r="F646" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G646" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H646" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B647" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C647" s="2" t="inlineStr">
+        <is>
+          <t>`input-clone-role-key` input</t>
+        </is>
+      </c>
+      <c r="D647" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E647" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'clone role key'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F647" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G647" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H647" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B648" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C648" s="2" t="inlineStr">
+        <is>
+          <t>`input-clone-role-label` input</t>
+        </is>
+      </c>
+      <c r="D648" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E648" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'clone role label'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F648" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G648" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H648" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B649" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C649" s="2" t="inlineStr">
+        <is>
+          <t>`input-create-email` input</t>
+        </is>
+      </c>
+      <c r="D649" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E649" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'create email'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F649" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G649" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H649" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B650" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C650" s="2" t="inlineStr">
+        <is>
+          <t>`input-create-name` input</t>
+        </is>
+      </c>
+      <c r="D650" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E650" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'create name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F650" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G650" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H650" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B651" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C651" s="2" t="inlineStr">
+        <is>
+          <t>`input-create-password` input</t>
+        </is>
+      </c>
+      <c r="D651" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E651" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'create password'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F651" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G651" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H651" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B652" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C652" s="2" t="inlineStr">
+        <is>
+          <t>`input-create-role-key` input</t>
+        </is>
+      </c>
+      <c r="D652" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E652" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'create role key'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F652" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G652" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H652" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B653" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C653" s="2" t="inlineStr">
+        <is>
+          <t>`input-create-role-label` input</t>
+        </is>
+      </c>
+      <c r="D653" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E653" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'create role label'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F653" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G653" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H653" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B654" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C654" s="2" t="inlineStr">
+        <is>
+          <t>`input-create-username` input</t>
+        </is>
+      </c>
+      <c r="D654" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E654" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'create username'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F654" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G654" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H654" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B655" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C655" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-password` input</t>
+        </is>
+      </c>
+      <c r="D655" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E655" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new password'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F655" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G655" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H655" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B656" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C656" s="2" t="inlineStr">
+        <is>
+          <t>`input-search-permissions` input</t>
+        </is>
+      </c>
+      <c r="D656" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E656" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'search permissions'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F656" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G656" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H656" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B657" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C657" s="2" t="inlineStr">
+        <is>
+          <t>`input-search-roles` input</t>
+        </is>
+      </c>
+      <c r="D657" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E657" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'search roles'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F657" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G657" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H657" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B658" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C658" s="2" t="inlineStr">
+        <is>
+          <t>`input-search-users` input</t>
+        </is>
+      </c>
+      <c r="D658" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E658" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'search users'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F658" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G658" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H658" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B659" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C659" s="2" t="inlineStr">
+        <is>
+          <t>`select-create-department` selector</t>
+        </is>
+      </c>
+      <c r="D659" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E659" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'create department'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F659" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G659" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H659" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B660" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C660" s="2" t="inlineStr">
+        <is>
+          <t>`select-create-role` selector</t>
+        </is>
+      </c>
+      <c r="D660" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E660" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'create role'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F660" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G660" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H660" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B661" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C661" s="2" t="inlineStr">
+        <is>
+          <t>`tab-audit` tab</t>
+        </is>
+      </c>
+      <c r="D661" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E661" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Admin Roles view to the 'audit' tab.</t>
+        </is>
+      </c>
+      <c r="F661" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G661" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H661" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B662" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C662" s="2" t="inlineStr">
+        <is>
+          <t>`tab-overrides` tab</t>
+        </is>
+      </c>
+      <c r="D662" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E662" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Admin Roles view to the 'overrides' tab.</t>
+        </is>
+      </c>
+      <c r="F662" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G662" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H662" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B663" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C663" s="2" t="inlineStr">
+        <is>
+          <t>`tab-pd-visibility` tab</t>
+        </is>
+      </c>
+      <c r="D663" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E663" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Admin Roles view to the 'pd visibility' tab.</t>
+        </is>
+      </c>
+      <c r="F663" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G663" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H663" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B664" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C664" s="2" t="inlineStr">
+        <is>
+          <t>`tab-roles` tab</t>
+        </is>
+      </c>
+      <c r="D664" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E664" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Admin Roles view to the 'roles' tab.</t>
+        </is>
+      </c>
+      <c r="F664" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G664" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H664" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B665" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C665" s="2" t="inlineStr">
+        <is>
+          <t>`tab-users` tab</t>
+        </is>
+      </c>
+      <c r="D665" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E665" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Admin Roles view to the 'users' tab.</t>
+        </is>
+      </c>
+      <c r="F665" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G665" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H665" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="inlineStr">
+        <is>
+          <t>Admin Roles</t>
+        </is>
+      </c>
+      <c r="B666" s="2" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="C666" s="2" t="inlineStr">
+        <is>
+          <t>`tab-workstream-visibility` tab</t>
+        </is>
+      </c>
+      <c r="D666" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E666" s="2" t="inlineStr">
+        <is>
+          <t>Switches the Admin Roles view to the 'workstream visibility' tab.</t>
+        </is>
+      </c>
+      <c r="F666" s="2" t="inlineStr">
+        <is>
+          <t>Switches local state; may trigger a new query.</t>
+        </is>
+      </c>
+      <c r="G666" s="2" t="inlineStr">
+        <is>
+          <t>Stays on the same URL.</t>
+        </is>
+      </c>
+      <c r="H666" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the tab's content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B667" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C667" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/ms-integration</t>
+        </is>
+      </c>
+      <c r="D667" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E667" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Role Settings (Admin) screen calls /api/admin/ms-integration to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F667" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G667" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Role Settings (Admin) page.</t>
+        </is>
+      </c>
+      <c r="H667" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B668" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C668" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/users/microsoft-mapping</t>
+        </is>
+      </c>
+      <c r="D668" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E668" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Role Settings (Admin) screen calls /api/admin/users/microsoft-mapping to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F668" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G668" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Role Settings (Admin) page.</t>
+        </is>
+      </c>
+      <c r="H668" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B669" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C669" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/ms-integration/status</t>
+        </is>
+      </c>
+      <c r="D669" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E669" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Role Settings (Admin) screen calls /api/ms-integration/status to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F669" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G669" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Role Settings (Admin) page.</t>
+        </is>
+      </c>
+      <c r="H669" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B670" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C670" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/outlook/status</t>
+        </is>
+      </c>
+      <c r="D670" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E670" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Role Settings (Admin) screen calls /api/outlook/status to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F670" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G670" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Role Settings (Admin) page.</t>
+        </is>
+      </c>
+      <c r="H670" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B671" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C671" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/procurement-analysis/run</t>
+        </is>
+      </c>
+      <c r="D671" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E671" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Role Settings (Admin) screen calls /api/procurement-analysis/run to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F671" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G671" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Role Settings (Admin) page.</t>
+        </is>
+      </c>
+      <c r="H671" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B672" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C672" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/procurement-analysis/status</t>
+        </is>
+      </c>
+      <c r="D672" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E672" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Role Settings (Admin) screen calls /api/procurement-analysis/status to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F672" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G672" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Role Settings (Admin) page.</t>
+        </is>
+      </c>
+      <c r="H672" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B673" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C673" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/role-auth/password</t>
+        </is>
+      </c>
+      <c r="D673" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E673" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Role Settings (Admin) screen calls /api/role-auth/password to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F673" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G673" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Role Settings (Admin) page.</t>
+        </is>
+      </c>
+      <c r="H673" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B674" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C674" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/role-auth/passwords</t>
+        </is>
+      </c>
+      <c r="D674" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E674" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Role Settings (Admin) screen calls /api/role-auth/passwords to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F674" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G674" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Role Settings (Admin) page.</t>
+        </is>
+      </c>
+      <c r="H674" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B675" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C675" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/settings?key={encodeURIComponent(key)}</t>
+        </is>
+      </c>
+      <c r="D675" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E675" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Role Settings (Admin) screen calls /api/settings?key={encodeURIComponent(key)} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F675" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G675" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Role Settings (Admin) page.</t>
+        </is>
+      </c>
+      <c r="H675" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B676" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C676" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/admin/users/{userId}/microsoft-id</t>
+        </is>
+      </c>
+      <c r="D676" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E676" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/admin/users/{userId}/microsoft-id when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F676" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G676" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H676" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B677" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C677" s="2" t="inlineStr">
+        <is>
+          <t>`button-add-tag` button</t>
+        </is>
+      </c>
+      <c r="D677" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E677" s="2" t="inlineStr">
+        <is>
+          <t>'Add tag' button — triggers the 'add tag' action on the Role Settings (Admin) screen.</t>
+        </is>
+      </c>
+      <c r="F677" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G677" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H677" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B678" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C678" s="2" t="inlineStr">
+        <is>
+          <t>`button-refresh-outlook` button</t>
+        </is>
+      </c>
+      <c r="D678" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E678" s="2" t="inlineStr">
+        <is>
+          <t>'Refresh outlook' button — triggers the 'refresh outlook' action on the Role Settings (Admin) screen.</t>
+        </is>
+      </c>
+      <c r="F678" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G678" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H678" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B679" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C679" s="2" t="inlineStr">
+        <is>
+          <t>`button-save-flags` button</t>
+        </is>
+      </c>
+      <c r="D679" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E679" s="2" t="inlineStr">
+        <is>
+          <t>'Save flags' button — triggers the 'save flags' action on the Role Settings (Admin) screen.</t>
+        </is>
+      </c>
+      <c r="F679" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G679" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H679" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B680" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C680" s="2" t="inlineStr">
+        <is>
+          <t>`button-save-ms-mapping` button</t>
+        </is>
+      </c>
+      <c r="D680" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E680" s="2" t="inlineStr">
+        <is>
+          <t>'Save ms mapping' button — triggers the 'save ms mapping' action on the Role Settings (Admin) screen.</t>
+        </is>
+      </c>
+      <c r="F680" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G680" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H680" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B681" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C681" s="2" t="inlineStr">
+        <is>
+          <t>`button-save-teams` button</t>
+        </is>
+      </c>
+      <c r="D681" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E681" s="2" t="inlineStr">
+        <is>
+          <t>'Save teams' button — triggers the 'save teams' action on the Role Settings (Admin) screen.</t>
+        </is>
+      </c>
+      <c r="F681" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G681" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H681" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B682" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C682" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-email` input</t>
+        </is>
+      </c>
+      <c r="D682" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E682" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit email'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F682" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G682" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H682" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B683" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C683" s="2" t="inlineStr">
+        <is>
+          <t>`input-edit-ms-id` input</t>
+        </is>
+      </c>
+      <c r="D683" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E683" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'edit ms id'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F683" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G683" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H683" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B684" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C684" s="2" t="inlineStr">
+        <is>
+          <t>`input-hot-hours` input</t>
+        </is>
+      </c>
+      <c r="D684" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E684" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'hot hours'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F684" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G684" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H684" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B685" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C685" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-tag` input</t>
+        </is>
+      </c>
+      <c r="D685" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E685" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new tag'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F685" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G685" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H685" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B686" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C686" s="2" t="inlineStr">
+        <is>
+          <t>`input-search-users` input</t>
+        </is>
+      </c>
+      <c r="D686" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E686" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'search users'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F686" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G686" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H686" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="2" t="inlineStr">
+        <is>
+          <t>Role Settings (Admin)</t>
+        </is>
+      </c>
+      <c r="B687" s="2" t="inlineStr">
+        <is>
+          <t>/admin/settings</t>
+        </is>
+      </c>
+      <c r="C687" s="2" t="inlineStr">
+        <is>
+          <t>`input-unanswered-hours` input</t>
+        </is>
+      </c>
+      <c r="D687" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E687" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'unanswered hours'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F687" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G687" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H687" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B688" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C688" s="2" t="inlineStr">
+        <is>
+          <t>`button-activate-template` button</t>
+        </is>
+      </c>
+      <c r="D688" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E688" s="2" t="inlineStr">
+        <is>
+          <t>'Activate template' button — triggers the 'activate template' action on the Phase Templates screen.</t>
+        </is>
+      </c>
+      <c r="F688" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G688" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H688" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B689" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C689" s="2" t="inlineStr">
+        <is>
+          <t>`button-add-eng-task` button</t>
+        </is>
+      </c>
+      <c r="D689" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E689" s="2" t="inlineStr">
+        <is>
+          <t>'Add eng task' button — triggers the 'add eng task' action on the Phase Templates screen.</t>
+        </is>
+      </c>
+      <c r="F689" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G689" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H689" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B690" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C690" s="2" t="inlineStr">
+        <is>
+          <t>`button-add-item` button</t>
+        </is>
+      </c>
+      <c r="D690" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E690" s="2" t="inlineStr">
+        <is>
+          <t>'Add item' button — triggers the 'add item' action on the Phase Templates screen.</t>
+        </is>
+      </c>
+      <c r="F690" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G690" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H690" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B691" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C691" s="2" t="inlineStr">
+        <is>
+          <t>`button-clone-template` button</t>
+        </is>
+      </c>
+      <c r="D691" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E691" s="2" t="inlineStr">
+        <is>
+          <t>'Clone template' button — triggers the 'clone template' action on the Phase Templates screen.</t>
+        </is>
+      </c>
+      <c r="F691" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G691" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H691" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B692" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C692" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-clone` button</t>
+        </is>
+      </c>
+      <c r="D692" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E692" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm clone' button — triggers the 'confirm clone' action on the Phase Templates screen.</t>
+        </is>
+      </c>
+      <c r="F692" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G692" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H692" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B693" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C693" s="2" t="inlineStr">
+        <is>
+          <t>`button-create-template` button</t>
+        </is>
+      </c>
+      <c r="D693" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E693" s="2" t="inlineStr">
+        <is>
+          <t>'Create template' button — triggers the 'create template' action on the Phase Templates screen.</t>
+        </is>
+      </c>
+      <c r="F693" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G693" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H693" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B694" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C694" s="2" t="inlineStr">
+        <is>
+          <t>`button-preview-template` button</t>
+        </is>
+      </c>
+      <c r="D694" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E694" s="2" t="inlineStr">
+        <is>
+          <t>'Preview template' button — triggers the 'preview template' action on the Phase Templates screen.</t>
+        </is>
+      </c>
+      <c r="F694" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G694" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H694" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B695" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C695" s="2" t="inlineStr">
+        <is>
+          <t>`button-save-item` button</t>
+        </is>
+      </c>
+      <c r="D695" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E695" s="2" t="inlineStr">
+        <is>
+          <t>'Save item' button — triggers the 'save item' action on the Phase Templates screen.</t>
+        </is>
+      </c>
+      <c r="F695" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G695" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H695" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B696" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C696" s="2" t="inlineStr">
+        <is>
+          <t>`button-save-template` button</t>
+        </is>
+      </c>
+      <c r="D696" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E696" s="2" t="inlineStr">
+        <is>
+          <t>'Save template' button — triggers the 'save template' action on the Phase Templates screen.</t>
+        </is>
+      </c>
+      <c r="F696" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G696" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H696" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B697" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C697" s="2" t="inlineStr">
+        <is>
+          <t>`input-item-description` input</t>
+        </is>
+      </c>
+      <c r="D697" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E697" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'item description'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F697" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G697" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H697" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B698" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C698" s="2" t="inlineStr">
+        <is>
+          <t>`input-item-key` input</t>
+        </is>
+      </c>
+      <c r="D698" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E698" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'item key'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F698" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G698" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H698" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B699" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C699" s="2" t="inlineStr">
+        <is>
+          <t>`input-item-sort` input</t>
+        </is>
+      </c>
+      <c r="D699" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E699" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'item sort'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F699" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G699" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H699" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B700" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C700" s="2" t="inlineStr">
+        <is>
+          <t>`input-item-title` input</t>
+        </is>
+      </c>
+      <c r="D700" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E700" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'item title'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F700" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G700" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H700" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B701" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C701" s="2" t="inlineStr">
+        <is>
+          <t>`input-template-name` input</t>
+        </is>
+      </c>
+      <c r="D701" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E701" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'template name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F701" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G701" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H701" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B702" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C702" s="2" t="inlineStr">
+        <is>
+          <t>`select-item-type` selector</t>
+        </is>
+      </c>
+      <c r="D702" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E702" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'item type'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F702" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G702" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H702" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="inlineStr">
+        <is>
+          <t>Phase Templates</t>
+        </is>
+      </c>
+      <c r="B703" s="2" t="inlineStr">
+        <is>
+          <t>/admin/phase-templates</t>
+        </is>
+      </c>
+      <c r="C703" s="2" t="inlineStr">
+        <is>
+          <t>`select-template-phase` selector</t>
+        </is>
+      </c>
+      <c r="D703" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E703" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'template phase'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F703" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G703" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H703" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="inlineStr">
+        <is>
+          <t>System Activity Log</t>
+        </is>
+      </c>
+      <c r="B704" s="2" t="inlineStr">
+        <is>
+          <t>/admin/activity-log</t>
+        </is>
+      </c>
+      <c r="C704" s="2" t="inlineStr">
+        <is>
+          <t>`button-activity-next` button</t>
+        </is>
+      </c>
+      <c r="D704" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E704" s="2" t="inlineStr">
+        <is>
+          <t>'Activity next' button — triggers the 'activity next' action on the System Activity Log screen.</t>
+        </is>
+      </c>
+      <c r="F704" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G704" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H704" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="inlineStr">
+        <is>
+          <t>System Activity Log</t>
+        </is>
+      </c>
+      <c r="B705" s="2" t="inlineStr">
+        <is>
+          <t>/admin/activity-log</t>
+        </is>
+      </c>
+      <c r="C705" s="2" t="inlineStr">
+        <is>
+          <t>`button-activity-prev` button</t>
+        </is>
+      </c>
+      <c r="D705" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E705" s="2" t="inlineStr">
+        <is>
+          <t>'Activity prev' button — triggers the 'activity prev' action on the System Activity Log screen.</t>
+        </is>
+      </c>
+      <c r="F705" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G705" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H705" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="inlineStr">
+        <is>
+          <t>System Activity Log</t>
+        </is>
+      </c>
+      <c r="B706" s="2" t="inlineStr">
+        <is>
+          <t>/admin/activity-log</t>
+        </is>
+      </c>
+      <c r="C706" s="2" t="inlineStr">
+        <is>
+          <t>`button-clear-filters` button</t>
+        </is>
+      </c>
+      <c r="D706" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E706" s="2" t="inlineStr">
+        <is>
+          <t>'Clear filters' button — triggers the 'clear filters' action on the System Activity Log screen.</t>
+        </is>
+      </c>
+      <c r="F706" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G706" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H706" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="inlineStr">
+        <is>
+          <t>System Activity Log</t>
+        </is>
+      </c>
+      <c r="B707" s="2" t="inlineStr">
+        <is>
+          <t>/admin/activity-log</t>
+        </is>
+      </c>
+      <c r="C707" s="2" t="inlineStr">
+        <is>
+          <t>`button-export-csv` button</t>
+        </is>
+      </c>
+      <c r="D707" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E707" s="2" t="inlineStr">
+        <is>
+          <t>'Export csv' button — triggers the 'export csv' action on the System Activity Log screen.</t>
+        </is>
+      </c>
+      <c r="F707" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G707" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H707" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="inlineStr">
+        <is>
+          <t>System Activity Log</t>
+        </is>
+      </c>
+      <c r="B708" s="2" t="inlineStr">
+        <is>
+          <t>/admin/activity-log</t>
+        </is>
+      </c>
+      <c r="C708" s="2" t="inlineStr">
+        <is>
+          <t>`input-activity-from-date` input</t>
+        </is>
+      </c>
+      <c r="D708" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E708" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'activity from date'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F708" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G708" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H708" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="inlineStr">
+        <is>
+          <t>System Activity Log</t>
+        </is>
+      </c>
+      <c r="B709" s="2" t="inlineStr">
+        <is>
+          <t>/admin/activity-log</t>
+        </is>
+      </c>
+      <c r="C709" s="2" t="inlineStr">
+        <is>
+          <t>`input-activity-search` input</t>
+        </is>
+      </c>
+      <c r="D709" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E709" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'activity search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F709" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G709" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H709" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="inlineStr">
+        <is>
+          <t>System Activity Log</t>
+        </is>
+      </c>
+      <c r="B710" s="2" t="inlineStr">
+        <is>
+          <t>/admin/activity-log</t>
+        </is>
+      </c>
+      <c r="C710" s="2" t="inlineStr">
+        <is>
+          <t>`input-activity-to-date` input</t>
+        </is>
+      </c>
+      <c r="D710" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E710" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'activity to date'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F710" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G710" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H710" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="2" t="inlineStr">
+        <is>
+          <t>System Activity Log</t>
+        </is>
+      </c>
+      <c r="B711" s="2" t="inlineStr">
+        <is>
+          <t>/admin/activity-log</t>
+        </is>
+      </c>
+      <c r="C711" s="2" t="inlineStr">
+        <is>
+          <t>`select-activity-action` selector</t>
+        </is>
+      </c>
+      <c r="D711" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E711" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'activity action'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F711" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G711" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H711" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="inlineStr">
+        <is>
+          <t>System Activity Log</t>
+        </is>
+      </c>
+      <c r="B712" s="2" t="inlineStr">
+        <is>
+          <t>/admin/activity-log</t>
+        </is>
+      </c>
+      <c r="C712" s="2" t="inlineStr">
+        <is>
+          <t>`select-activity-entity` selector</t>
+        </is>
+      </c>
+      <c r="D712" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E712" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'activity entity'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F712" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G712" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H712" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="inlineStr">
+        <is>
+          <t>System Activity Log</t>
+        </is>
+      </c>
+      <c r="B713" s="2" t="inlineStr">
+        <is>
+          <t>/admin/activity-log</t>
+        </is>
+      </c>
+      <c r="C713" s="2" t="inlineStr">
+        <is>
+          <t>`select-activity-project` selector</t>
+        </is>
+      </c>
+      <c r="D713" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E713" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'activity project'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F713" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G713" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H713" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="inlineStr">
+        <is>
+          <t>System Activity Log</t>
+        </is>
+      </c>
+      <c r="B714" s="2" t="inlineStr">
+        <is>
+          <t>/admin/activity-log</t>
+        </is>
+      </c>
+      <c r="C714" s="2" t="inlineStr">
+        <is>
+          <t>`select-activity-source` selector</t>
+        </is>
+      </c>
+      <c r="D714" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E714" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'activity source'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F714" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G714" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H714" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="inlineStr">
+        <is>
+          <t>System Activity Log</t>
+        </is>
+      </c>
+      <c r="B715" s="2" t="inlineStr">
+        <is>
+          <t>/admin/activity-log</t>
+        </is>
+      </c>
+      <c r="C715" s="2" t="inlineStr">
+        <is>
+          <t>`select-activity-user` selector</t>
+        </is>
+      </c>
+      <c r="D715" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E715" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'activity user'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F715" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G715" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H715" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="inlineStr">
+        <is>
+          <t>Database Migration</t>
+        </is>
+      </c>
+      <c r="B716" s="2" t="inlineStr">
+        <is>
+          <t>/admin/database-migration</t>
+        </is>
+      </c>
+      <c r="C716" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/migration/check-references</t>
+        </is>
+      </c>
+      <c r="D716" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E716" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Database Migration screen calls /api/admin/migration/check-references to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F716" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G716" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Database Migration page.</t>
+        </is>
+      </c>
+      <c r="H716" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="2" t="inlineStr">
+        <is>
+          <t>Database Migration</t>
+        </is>
+      </c>
+      <c r="B717" s="2" t="inlineStr">
+        <is>
+          <t>/admin/database-migration</t>
+        </is>
+      </c>
+      <c r="C717" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/migration/status</t>
+        </is>
+      </c>
+      <c r="D717" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E717" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Database Migration screen calls /api/admin/migration/status to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F717" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G717" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Database Migration page.</t>
+        </is>
+      </c>
+      <c r="H717" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="inlineStr">
+        <is>
+          <t>Database Migration</t>
+        </is>
+      </c>
+      <c r="B718" s="2" t="inlineStr">
+        <is>
+          <t>/admin/database-migration</t>
+        </is>
+      </c>
+      <c r="C718" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/migration/verify</t>
+        </is>
+      </c>
+      <c r="D718" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E718" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Database Migration screen calls /api/admin/migration/verify to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F718" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G718" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Database Migration page.</t>
+        </is>
+      </c>
+      <c r="H718" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="inlineStr">
+        <is>
+          <t>Database Migration</t>
+        </is>
+      </c>
+      <c r="B719" s="2" t="inlineStr">
+        <is>
+          <t>/admin/database-migration</t>
+        </is>
+      </c>
+      <c r="C719" s="2" t="inlineStr">
+        <is>
+          <t>`input-archive-confirm` input</t>
+        </is>
+      </c>
+      <c r="D719" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E719" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'archive confirm'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F719" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G719" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H719" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="inlineStr">
+        <is>
+          <t>Database Migration</t>
+        </is>
+      </c>
+      <c r="B720" s="2" t="inlineStr">
+        <is>
+          <t>/admin/database-migration</t>
+        </is>
+      </c>
+      <c r="C720" s="2" t="inlineStr">
+        <is>
+          <t>`input-backup-desc` input</t>
+        </is>
+      </c>
+      <c r="D720" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E720" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'backup desc'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F720" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G720" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H720" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="2" t="inlineStr">
+        <is>
+          <t>Database Migration</t>
+        </is>
+      </c>
+      <c r="B721" s="2" t="inlineStr">
+        <is>
+          <t>/admin/database-migration</t>
+        </is>
+      </c>
+      <c r="C721" s="2" t="inlineStr">
+        <is>
+          <t>`input-backup-id` input</t>
+        </is>
+      </c>
+      <c r="D721" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E721" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'backup id'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F721" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G721" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H721" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="2" t="inlineStr">
+        <is>
+          <t>Database Migration</t>
+        </is>
+      </c>
+      <c r="B722" s="2" t="inlineStr">
+        <is>
+          <t>/admin/database-migration</t>
+        </is>
+      </c>
+      <c r="C722" s="2" t="inlineStr">
+        <is>
+          <t>`input-drop-confirm` input</t>
+        </is>
+      </c>
+      <c r="D722" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E722" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'drop confirm'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F722" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G722" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H722" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="2" t="inlineStr">
+        <is>
+          <t>Import Control Tower</t>
+        </is>
+      </c>
+      <c r="B723" s="2" t="inlineStr">
+        <is>
+          <t>/admin/import-control-tower</t>
+        </is>
+      </c>
+      <c r="C723" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/import-control-tower/history</t>
+        </is>
+      </c>
+      <c r="D723" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E723" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Import Control Tower screen calls /api/import-control-tower/history to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F723" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G723" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Import Control Tower page.</t>
+        </is>
+      </c>
+      <c r="H723" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="inlineStr">
+        <is>
+          <t>Import Control Tower</t>
+        </is>
+      </c>
+      <c r="B724" s="2" t="inlineStr">
+        <is>
+          <t>/admin/import-control-tower</t>
+        </is>
+      </c>
+      <c r="C724" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/import-control-tower/history?{params.toString()}</t>
+        </is>
+      </c>
+      <c r="D724" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E724" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Import Control Tower screen calls /api/import-control-tower/history?{params.toString()} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F724" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G724" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Import Control Tower page.</t>
+        </is>
+      </c>
+      <c r="H724" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="2" t="inlineStr">
+        <is>
+          <t>Import Control Tower</t>
+        </is>
+      </c>
+      <c r="B725" s="2" t="inlineStr">
+        <is>
+          <t>/admin/import-control-tower</t>
+        </is>
+      </c>
+      <c r="C725" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/import-control-tower/retry/{runId}</t>
+        </is>
+      </c>
+      <c r="D725" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E725" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Import Control Tower screen calls /api/import-control-tower/retry/{runId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F725" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G725" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Import Control Tower page.</t>
+        </is>
+      </c>
+      <c r="H725" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="2" t="inlineStr">
+        <is>
+          <t>Import Control Tower</t>
+        </is>
+      </c>
+      <c r="B726" s="2" t="inlineStr">
+        <is>
+          <t>/admin/import-control-tower</t>
+        </is>
+      </c>
+      <c r="C726" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/import-control-tower/run</t>
+        </is>
+      </c>
+      <c r="D726" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E726" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Import Control Tower screen calls /api/import-control-tower/run to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F726" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G726" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Import Control Tower page.</t>
+        </is>
+      </c>
+      <c r="H726" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="2" t="inlineStr">
+        <is>
+          <t>Import Control Tower</t>
+        </is>
+      </c>
+      <c r="B727" s="2" t="inlineStr">
+        <is>
+          <t>/admin/import-control-tower</t>
+        </is>
+      </c>
+      <c r="C727" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/import-control-tower/run/{selectedRunId}/errors</t>
+        </is>
+      </c>
+      <c r="D727" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E727" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Import Control Tower screen calls /api/import-control-tower/run/{selectedRunId}/errors to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F727" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G727" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Import Control Tower page.</t>
+        </is>
+      </c>
+      <c r="H727" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="inlineStr">
+        <is>
+          <t>Import Control Tower</t>
+        </is>
+      </c>
+      <c r="B728" s="2" t="inlineStr">
+        <is>
+          <t>/admin/import-control-tower</t>
+        </is>
+      </c>
+      <c r="C728" s="2" t="inlineStr">
+        <is>
+          <t>`button-refresh` button</t>
+        </is>
+      </c>
+      <c r="D728" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E728" s="2" t="inlineStr">
+        <is>
+          <t>'Refresh' button — triggers the 'refresh' action on the Import Control Tower screen.</t>
+        </is>
+      </c>
+      <c r="F728" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G728" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H728" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="2" t="inlineStr">
+        <is>
+          <t>Import Control Tower</t>
+        </is>
+      </c>
+      <c r="B729" s="2" t="inlineStr">
+        <is>
+          <t>/admin/import-control-tower</t>
+        </is>
+      </c>
+      <c r="C729" s="2" t="inlineStr">
+        <is>
+          <t>`select-status-filter` selector</t>
+        </is>
+      </c>
+      <c r="D729" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E729" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'status filter'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F729" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G729" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H729" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="inlineStr">
+        <is>
+          <t>Import Control Tower</t>
+        </is>
+      </c>
+      <c r="B730" s="2" t="inlineStr">
+        <is>
+          <t>/admin/import-control-tower</t>
+        </is>
+      </c>
+      <c r="C730" s="2" t="inlineStr">
+        <is>
+          <t>`select-type-filter` selector</t>
+        </is>
+      </c>
+      <c r="D730" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E730" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'type filter'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F730" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G730" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H730" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="inlineStr">
+        <is>
+          <t>KPI Traceability</t>
+        </is>
+      </c>
+      <c r="B731" s="2" t="inlineStr">
+        <is>
+          <t>/admin/kpi-traceability</t>
+        </is>
+      </c>
+      <c r="C731" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/kpi-traceability</t>
+        </is>
+      </c>
+      <c r="D731" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E731" s="2" t="inlineStr">
+        <is>
+          <t>On load, the KPI Traceability screen calls /api/admin/kpi-traceability to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F731" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G731" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the KPI Traceability page.</t>
+        </is>
+      </c>
+      <c r="H731" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="inlineStr">
+        <is>
+          <t>KPI Traceability</t>
+        </is>
+      </c>
+      <c r="B732" s="2" t="inlineStr">
+        <is>
+          <t>/admin/kpi-traceability</t>
+        </is>
+      </c>
+      <c r="C732" s="2" t="inlineStr">
+        <is>
+          <t>`button-refresh-kpi` button</t>
+        </is>
+      </c>
+      <c r="D732" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E732" s="2" t="inlineStr">
+        <is>
+          <t>'Refresh kpi' button — triggers the 'refresh kpi' action on the KPI Traceability screen.</t>
+        </is>
+      </c>
+      <c r="F732" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G732" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H732" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="2" t="inlineStr">
+        <is>
+          <t>KPI Traceability</t>
+        </is>
+      </c>
+      <c r="B733" s="2" t="inlineStr">
+        <is>
+          <t>/admin/kpi-traceability</t>
+        </is>
+      </c>
+      <c r="C733" s="2" t="inlineStr">
+        <is>
+          <t>`input-kpi-search` input</t>
+        </is>
+      </c>
+      <c r="D733" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E733" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'kpi search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F733" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G733" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H733" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="inlineStr">
+        <is>
+          <t>Stage Admin Panel</t>
+        </is>
+      </c>
+      <c r="B734" s="2" t="inlineStr">
+        <is>
+          <t>/admin/stage-lifecycle</t>
+        </is>
+      </c>
+      <c r="C734" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/stage-checklist-templates</t>
+        </is>
+      </c>
+      <c r="D734" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E734" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Stage Admin Panel screen calls /api/admin/stage-checklist-templates to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F734" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G734" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Stage Admin Panel page.</t>
+        </is>
+      </c>
+      <c r="H734" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="2" t="inlineStr">
+        <is>
+          <t>Stage Admin Panel</t>
+        </is>
+      </c>
+      <c r="B735" s="2" t="inlineStr">
+        <is>
+          <t>/admin/stage-lifecycle</t>
+        </is>
+      </c>
+      <c r="C735" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/admin/stage-definitions</t>
+        </is>
+      </c>
+      <c r="D735" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E735" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Stage Admin Panel screen calls /api/admin/stage-definitions to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F735" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G735" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Stage Admin Panel page.</t>
+        </is>
+      </c>
+      <c r="H735" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="inlineStr">
+        <is>
+          <t>Stage Admin Panel</t>
+        </is>
+      </c>
+      <c r="B736" s="2" t="inlineStr">
+        <is>
+          <t>/admin/stage-lifecycle</t>
+        </is>
+      </c>
+      <c r="C736" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/admin/stage-checklist-templates/{template.id}</t>
+        </is>
+      </c>
+      <c r="D736" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E736" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/admin/stage-checklist-templates/{template.id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F736" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G736" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H736" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="2" t="inlineStr">
+        <is>
+          <t>Stage Admin Panel</t>
+        </is>
+      </c>
+      <c r="B737" s="2" t="inlineStr">
+        <is>
+          <t>/admin/stage-lifecycle</t>
+        </is>
+      </c>
+      <c r="C737" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/admin/stage-definitions/{def.id}</t>
+        </is>
+      </c>
+      <c r="D737" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E737" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/admin/stage-definitions/{def.id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F737" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G737" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H737" s="2" t="inlineStr">
         <is>
           <t>See Data Sources sheet for the handler + tables.</t>
         </is>

--- a/docs/workbook/emergent-energy-system-map.xlsx
+++ b/docs/workbook/emergent-energy-system-map.xlsx
@@ -5722,7 +5722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H737"/>
+  <dimension ref="A1:H908"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -36684,6 +36684,7188 @@
         </is>
       </c>
       <c r="H737" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="2" t="inlineStr">
+        <is>
+          <t>My Work Home</t>
+        </is>
+      </c>
+      <c r="B738" s="2" t="inlineStr">
+        <is>
+          <t>/my-work</t>
+        </is>
+      </c>
+      <c r="C738" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/approvals/pending</t>
+        </is>
+      </c>
+      <c r="D738" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E738" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Home screen calls /api/approvals/pending to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F738" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G738" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Home page.</t>
+        </is>
+      </c>
+      <c r="H738" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="2" t="inlineStr">
+        <is>
+          <t>My Work Home</t>
+        </is>
+      </c>
+      <c r="B739" s="2" t="inlineStr">
+        <is>
+          <t>/my-work</t>
+        </is>
+      </c>
+      <c r="C739" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/approvals/pending-count</t>
+        </is>
+      </c>
+      <c r="D739" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E739" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Home screen calls /api/approvals/pending-count to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F739" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G739" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Home page.</t>
+        </is>
+      </c>
+      <c r="H739" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="inlineStr">
+        <is>
+          <t>My Work Home</t>
+        </is>
+      </c>
+      <c r="B740" s="2" t="inlineStr">
+        <is>
+          <t>/my-work</t>
+        </is>
+      </c>
+      <c r="C740" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/ms-objects/mine</t>
+        </is>
+      </c>
+      <c r="D740" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E740" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Home screen calls /api/ms-objects/mine to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F740" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G740" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Home page.</t>
+        </is>
+      </c>
+      <c r="H740" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="2" t="inlineStr">
+        <is>
+          <t>My Work Home</t>
+        </is>
+      </c>
+      <c r="B741" s="2" t="inlineStr">
+        <is>
+          <t>/my-work</t>
+        </is>
+      </c>
+      <c r="C741" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/ms-objects/mine?action_required=true</t>
+        </is>
+      </c>
+      <c r="D741" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E741" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Home screen calls /api/ms-objects/mine?action_required=true to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F741" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G741" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Home page.</t>
+        </is>
+      </c>
+      <c r="H741" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="inlineStr">
+        <is>
+          <t>My Work Home</t>
+        </is>
+      </c>
+      <c r="B742" s="2" t="inlineStr">
+        <is>
+          <t>/my-work</t>
+        </is>
+      </c>
+      <c r="C742" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/ms-sync/trigger</t>
+        </is>
+      </c>
+      <c r="D742" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E742" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Home screen calls /api/ms-sync/trigger to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F742" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G742" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Home page.</t>
+        </is>
+      </c>
+      <c r="H742" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="2" t="inlineStr">
+        <is>
+          <t>My Work Home</t>
+        </is>
+      </c>
+      <c r="B743" s="2" t="inlineStr">
+        <is>
+          <t>/my-work</t>
+        </is>
+      </c>
+      <c r="C743" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/ms-teams/chats</t>
+        </is>
+      </c>
+      <c r="D743" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E743" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Home screen calls /api/ms-teams/chats to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F743" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G743" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Home page.</t>
+        </is>
+      </c>
+      <c r="H743" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="inlineStr">
+        <is>
+          <t>My Work Home</t>
+        </is>
+      </c>
+      <c r="B744" s="2" t="inlineStr">
+        <is>
+          <t>/my-work</t>
+        </is>
+      </c>
+      <c r="C744" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/my-work/all-tasks</t>
+        </is>
+      </c>
+      <c r="D744" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E744" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Home screen calls /api/my-work/all-tasks to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F744" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G744" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Home page.</t>
+        </is>
+      </c>
+      <c r="H744" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="2" t="inlineStr">
+        <is>
+          <t>My Work Home</t>
+        </is>
+      </c>
+      <c r="B745" s="2" t="inlineStr">
+        <is>
+          <t>/my-work</t>
+        </is>
+      </c>
+      <c r="C745" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/mytool/escalated-priorities</t>
+        </is>
+      </c>
+      <c r="D745" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E745" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Home screen calls /api/mytool/escalated-priorities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F745" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G745" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Home page.</t>
+        </is>
+      </c>
+      <c r="H745" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="inlineStr">
+        <is>
+          <t>My Work Home</t>
+        </is>
+      </c>
+      <c r="B746" s="2" t="inlineStr">
+        <is>
+          <t>/my-work</t>
+        </is>
+      </c>
+      <c r="C746" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/outlook/events?start={today}&amp;end={today}</t>
+        </is>
+      </c>
+      <c r="D746" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E746" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Home screen calls /api/outlook/events?start={today}&amp;end={today} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F746" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G746" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Home page.</t>
+        </is>
+      </c>
+      <c r="H746" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="2" t="inlineStr">
+        <is>
+          <t>My Work Home</t>
+        </is>
+      </c>
+      <c r="B747" s="2" t="inlineStr">
+        <is>
+          <t>/my-work</t>
+        </is>
+      </c>
+      <c r="C747" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/outlook/status</t>
+        </is>
+      </c>
+      <c r="D747" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E747" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Home screen calls /api/outlook/status to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F747" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G747" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Home page.</t>
+        </is>
+      </c>
+      <c r="H747" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="inlineStr">
+        <is>
+          <t>My Work Home</t>
+        </is>
+      </c>
+      <c r="B748" s="2" t="inlineStr">
+        <is>
+          <t>/my-work</t>
+        </is>
+      </c>
+      <c r="C748" s="2" t="inlineStr">
+        <is>
+          <t>`button-refresh-tasks` button</t>
+        </is>
+      </c>
+      <c r="D748" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E748" s="2" t="inlineStr">
+        <is>
+          <t>'Refresh tasks' button — triggers the 'refresh tasks' action on the My Work Home screen.</t>
+        </is>
+      </c>
+      <c r="F748" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G748" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H748" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="2" t="inlineStr">
+        <is>
+          <t>My Work Home</t>
+        </is>
+      </c>
+      <c r="B749" s="2" t="inlineStr">
+        <is>
+          <t>/my-work</t>
+        </is>
+      </c>
+      <c r="C749" s="2" t="inlineStr">
+        <is>
+          <t>`button-sync-all` button</t>
+        </is>
+      </c>
+      <c r="D749" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E749" s="2" t="inlineStr">
+        <is>
+          <t>'Sync all' button — triggers the 'sync all' action on the My Work Home screen.</t>
+        </is>
+      </c>
+      <c r="F749" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G749" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H749" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="inlineStr">
+        <is>
+          <t>My Work Home</t>
+        </is>
+      </c>
+      <c r="B750" s="2" t="inlineStr">
+        <is>
+          <t>/my-work</t>
+        </is>
+      </c>
+      <c r="C750" s="2" t="inlineStr">
+        <is>
+          <t>`link-all-tasks` link</t>
+        </is>
+      </c>
+      <c r="D750" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E750" s="2" t="inlineStr">
+        <is>
+          <t>Navigates to the 'all tasks' destination.</t>
+        </is>
+      </c>
+      <c r="F750" s="2" t="inlineStr">
+        <is>
+          <t>Nothing on click.</t>
+        </is>
+      </c>
+      <c r="G750" s="2" t="inlineStr">
+        <is>
+          <t>Varies — see source.</t>
+        </is>
+      </c>
+      <c r="H750" s="2" t="inlineStr">
+        <is>
+          <t>None on click.</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="2" t="inlineStr">
+        <is>
+          <t>My Work Home</t>
+        </is>
+      </c>
+      <c r="B751" s="2" t="inlineStr">
+        <is>
+          <t>/my-work</t>
+        </is>
+      </c>
+      <c r="C751" s="2" t="inlineStr">
+        <is>
+          <t>`link-full-calendar` link</t>
+        </is>
+      </c>
+      <c r="D751" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E751" s="2" t="inlineStr">
+        <is>
+          <t>Navigates to the 'full calendar' destination.</t>
+        </is>
+      </c>
+      <c r="F751" s="2" t="inlineStr">
+        <is>
+          <t>Nothing on click.</t>
+        </is>
+      </c>
+      <c r="G751" s="2" t="inlineStr">
+        <is>
+          <t>Varies — see source.</t>
+        </is>
+      </c>
+      <c r="H751" s="2" t="inlineStr">
+        <is>
+          <t>None on click.</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="inlineStr">
+        <is>
+          <t>My Work Calendar</t>
+        </is>
+      </c>
+      <c r="B752" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/calendar</t>
+        </is>
+      </c>
+      <c r="C752" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/calendar/schedule-task</t>
+        </is>
+      </c>
+      <c r="D752" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E752" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Calendar screen calls /api/calendar/schedule-task to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F752" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G752" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Calendar page.</t>
+        </is>
+      </c>
+      <c r="H752" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="2" t="inlineStr">
+        <is>
+          <t>My Work Calendar</t>
+        </is>
+      </c>
+      <c r="B753" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/calendar</t>
+        </is>
+      </c>
+      <c r="C753" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/ms-objects/mine</t>
+        </is>
+      </c>
+      <c r="D753" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E753" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Calendar screen calls /api/ms-objects/mine to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F753" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G753" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Calendar page.</t>
+        </is>
+      </c>
+      <c r="H753" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="inlineStr">
+        <is>
+          <t>My Work Calendar</t>
+        </is>
+      </c>
+      <c r="B754" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/calendar</t>
+        </is>
+      </c>
+      <c r="C754" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/ms-objects/mine?action_required=true</t>
+        </is>
+      </c>
+      <c r="D754" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E754" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Calendar screen calls /api/ms-objects/mine?action_required=true to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F754" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G754" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Calendar page.</t>
+        </is>
+      </c>
+      <c r="H754" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="2" t="inlineStr">
+        <is>
+          <t>My Work Calendar</t>
+        </is>
+      </c>
+      <c r="B755" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/calendar</t>
+        </is>
+      </c>
+      <c r="C755" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/ms-sync/trigger</t>
+        </is>
+      </c>
+      <c r="D755" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E755" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Calendar screen calls /api/ms-sync/trigger to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F755" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G755" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Calendar page.</t>
+        </is>
+      </c>
+      <c r="H755" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="inlineStr">
+        <is>
+          <t>My Work Calendar</t>
+        </is>
+      </c>
+      <c r="B756" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/calendar</t>
+        </is>
+      </c>
+      <c r="C756" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/my-work/all-tasks</t>
+        </is>
+      </c>
+      <c r="D756" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E756" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Calendar screen calls /api/my-work/all-tasks to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F756" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G756" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Calendar page.</t>
+        </is>
+      </c>
+      <c r="H756" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="2" t="inlineStr">
+        <is>
+          <t>My Work Calendar</t>
+        </is>
+      </c>
+      <c r="B757" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/calendar</t>
+        </is>
+      </c>
+      <c r="C757" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/outlook/events?start={startStr}&amp;end={endStr}</t>
+        </is>
+      </c>
+      <c r="D757" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E757" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Calendar screen calls /api/outlook/events?start={startStr}&amp;end={endStr} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F757" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G757" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Calendar page.</t>
+        </is>
+      </c>
+      <c r="H757" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="inlineStr">
+        <is>
+          <t>My Work Calendar</t>
+        </is>
+      </c>
+      <c r="B758" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/calendar</t>
+        </is>
+      </c>
+      <c r="C758" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/outlook/status</t>
+        </is>
+      </c>
+      <c r="D758" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E758" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Calendar screen calls /api/outlook/status to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F758" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G758" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Calendar page.</t>
+        </is>
+      </c>
+      <c r="H758" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="2" t="inlineStr">
+        <is>
+          <t>My Work Calendar</t>
+        </is>
+      </c>
+      <c r="B759" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/calendar</t>
+        </is>
+      </c>
+      <c r="C759" s="2" t="inlineStr">
+        <is>
+          <t>`button-refresh-connection` button</t>
+        </is>
+      </c>
+      <c r="D759" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E759" s="2" t="inlineStr">
+        <is>
+          <t>'Refresh connection' button — triggers the 'refresh connection' action on the My Work Calendar screen.</t>
+        </is>
+      </c>
+      <c r="F759" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G759" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H759" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B760" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C760" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /api/mytool/tasks/{id}</t>
+        </is>
+      </c>
+      <c r="D760" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E760" s="2" t="inlineStr">
+        <is>
+          <t>Sends a DELETE to /api/mytool/tasks/{id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F760" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G760" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H760" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B761" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C761" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/eng/tasks</t>
+        </is>
+      </c>
+      <c r="D761" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E761" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/eng/tasks to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F761" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G761" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H761" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B762" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C762" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/eng/tasks/{parentId}/subtasks</t>
+        </is>
+      </c>
+      <c r="D762" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E762" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/eng/tasks/{parentId}/subtasks to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F762" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G762" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H762" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B763" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C763" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/eng/tasks/{task.id}/subtasks</t>
+        </is>
+      </c>
+      <c r="D763" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E763" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/eng/tasks/{task.id}/subtasks to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F763" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G763" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H763" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B764" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C764" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/ms-objects/{task._rawId}/dismiss</t>
+        </is>
+      </c>
+      <c r="D764" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E764" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/ms-objects/{task._rawId}/dismiss to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F764" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G764" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H764" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B765" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C765" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/ms-objects/mine</t>
+        </is>
+      </c>
+      <c r="D765" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E765" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/ms-objects/mine to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F765" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G765" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H765" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B766" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C766" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/my-work/all-tasks</t>
+        </is>
+      </c>
+      <c r="D766" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E766" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/my-work/all-tasks to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F766" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G766" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H766" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B767" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C767" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/operational-tasks/{task._rawId}</t>
+        </is>
+      </c>
+      <c r="D767" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E767" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/operational-tasks/{task._rawId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F767" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G767" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H767" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B768" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C768" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/planning-tasks</t>
+        </is>
+      </c>
+      <c r="D768" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E768" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/planning-tasks to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F768" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G768" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H768" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B769" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C769" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/planning-tasks/{task._rawId}</t>
+        </is>
+      </c>
+      <c r="D769" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E769" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/planning-tasks/{task._rawId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F769" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G769" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H769" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B770" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C770" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/project-info</t>
+        </is>
+      </c>
+      <c r="D770" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E770" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/project-info to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F770" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G770" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H770" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B771" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C771" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(page load) GET /api/quality/project/{encodeURIComponent(task.projectName || </t>
+        </is>
+      </c>
+      <c r="D771" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E771" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/quality/project/{encodeURIComponent(task.projectName ||  to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F771" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G771" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H771" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B772" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C772" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/task-checklist-items/{task._rawId}</t>
+        </is>
+      </c>
+      <c r="D772" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E772" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/task-checklist-items/{task._rawId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F772" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G772" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H772" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B773" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C773" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/task-comments</t>
+        </is>
+      </c>
+      <c r="D773" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E773" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/task-comments to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F773" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G773" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H773" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B774" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C774" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/tasks/reassign</t>
+        </is>
+      </c>
+      <c r="D774" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E774" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/tasks/reassign to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F774" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G774" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H774" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B775" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C775" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/tr-register</t>
+        </is>
+      </c>
+      <c r="D775" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E775" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/tr-register to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F775" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G775" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H775" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B776" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C776" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/tr-register/{task._rawId}</t>
+        </is>
+      </c>
+      <c r="D776" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E776" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/tr-register/{task._rawId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F776" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G776" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H776" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B777" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C777" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/users/assignable</t>
+        </is>
+      </c>
+      <c r="D777" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E777" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/users/assignable to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F777" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G777" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H777" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B778" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C778" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/work-items/{taskId}/viewers</t>
+        </is>
+      </c>
+      <c r="D778" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E778" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Tasks screen calls /api/work-items/{taskId}/viewers to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F778" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G778" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Tasks page.</t>
+        </is>
+      </c>
+      <c r="H778" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B779" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C779" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/mytool/tasks/{id}</t>
+        </is>
+      </c>
+      <c r="D779" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E779" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/mytool/tasks/{id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F779" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G779" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H779" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B780" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C780" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/mytool/tasks/{task._rawId}</t>
+        </is>
+      </c>
+      <c r="D780" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E780" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/mytool/tasks/{task._rawId} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F780" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G780" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H780" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B781" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C781" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/mytool/tasks</t>
+        </is>
+      </c>
+      <c r="D781" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E781" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/mytool/tasks when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F781" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G781" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H781" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B782" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C782" s="2" t="inlineStr">
+        <is>
+          <t>`button-cancel-create` button</t>
+        </is>
+      </c>
+      <c r="D782" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E782" s="2" t="inlineStr">
+        <is>
+          <t>'Cancel create' button — triggers the 'cancel create' action on the My Work Tasks screen.</t>
+        </is>
+      </c>
+      <c r="F782" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G782" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H782" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B783" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C783" s="2" t="inlineStr">
+        <is>
+          <t>`button-cancel-subtask` button</t>
+        </is>
+      </c>
+      <c r="D783" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E783" s="2" t="inlineStr">
+        <is>
+          <t>'Cancel subtask' button — triggers the 'cancel subtask' action on the My Work Tasks screen.</t>
+        </is>
+      </c>
+      <c r="F783" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G783" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H783" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B784" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C784" s="2" t="inlineStr">
+        <is>
+          <t>`button-clear-all-filters` button</t>
+        </is>
+      </c>
+      <c r="D784" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E784" s="2" t="inlineStr">
+        <is>
+          <t>'Clear all filters' button — triggers the 'clear all filters' action on the My Work Tasks screen.</t>
+        </is>
+      </c>
+      <c r="F784" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G784" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H784" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B785" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C785" s="2" t="inlineStr">
+        <is>
+          <t>`button-create-subtask` button</t>
+        </is>
+      </c>
+      <c r="D785" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E785" s="2" t="inlineStr">
+        <is>
+          <t>'Create subtask' button — triggers the 'create subtask' action on the My Work Tasks screen.</t>
+        </is>
+      </c>
+      <c r="F785" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G785" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H785" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B786" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C786" s="2" t="inlineStr">
+        <is>
+          <t>`button-groom-mode` button</t>
+        </is>
+      </c>
+      <c r="D786" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E786" s="2" t="inlineStr">
+        <is>
+          <t>'Groom mode' button — triggers the 'groom mode' action on the My Work Tasks screen.</t>
+        </is>
+      </c>
+      <c r="F786" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G786" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H786" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B787" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C787" s="2" t="inlineStr">
+        <is>
+          <t>`button-new-task` button</t>
+        </is>
+      </c>
+      <c r="D787" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E787" s="2" t="inlineStr">
+        <is>
+          <t>'New task' button — triggers the 'new task' action on the My Work Tasks screen.</t>
+        </is>
+      </c>
+      <c r="F787" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G787" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H787" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B788" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C788" s="2" t="inlineStr">
+        <is>
+          <t>`button-open-origin-context` button</t>
+        </is>
+      </c>
+      <c r="D788" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E788" s="2" t="inlineStr">
+        <is>
+          <t>'Open origin context' button — triggers the 'open origin context' action on the My Work Tasks screen.</t>
+        </is>
+      </c>
+      <c r="F788" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G788" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H788" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B789" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C789" s="2" t="inlineStr">
+        <is>
+          <t>`button-open-project-context` button</t>
+        </is>
+      </c>
+      <c r="D789" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E789" s="2" t="inlineStr">
+        <is>
+          <t>'Open project context' button — triggers the 'open project context' action on the My Work Tasks screen.</t>
+        </is>
+      </c>
+      <c r="F789" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G789" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H789" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B790" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C790" s="2" t="inlineStr">
+        <is>
+          <t>`button-open-source-context` button</t>
+        </is>
+      </c>
+      <c r="D790" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E790" s="2" t="inlineStr">
+        <is>
+          <t>'Open source context' button — triggers the 'open source context' action on the My Work Tasks screen.</t>
+        </is>
+      </c>
+      <c r="F790" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G790" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H790" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B791" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C791" s="2" t="inlineStr">
+        <is>
+          <t>`button-show-completed` button</t>
+        </is>
+      </c>
+      <c r="D791" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E791" s="2" t="inlineStr">
+        <is>
+          <t>'Show completed' button — triggers the 'show completed' action on the My Work Tasks screen.</t>
+        </is>
+      </c>
+      <c r="F791" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G791" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H791" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B792" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C792" s="2" t="inlineStr">
+        <is>
+          <t>`button-submit-create` button</t>
+        </is>
+      </c>
+      <c r="D792" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E792" s="2" t="inlineStr">
+        <is>
+          <t>'Submit create' button — triggers the 'submit create' action on the My Work Tasks screen.</t>
+        </is>
+      </c>
+      <c r="F792" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G792" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H792" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B793" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C793" s="2" t="inlineStr">
+        <is>
+          <t>`button-toggle-filters` button</t>
+        </is>
+      </c>
+      <c r="D793" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E793" s="2" t="inlineStr">
+        <is>
+          <t>'Toggle filters' button — triggers the 'toggle filters' action on the My Work Tasks screen.</t>
+        </is>
+      </c>
+      <c r="F793" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G793" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H793" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B794" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C794" s="2" t="inlineStr">
+        <is>
+          <t>`input-assign-search` input</t>
+        </is>
+      </c>
+      <c r="D794" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E794" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'assign search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F794" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G794" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H794" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B795" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C795" s="2" t="inlineStr">
+        <is>
+          <t>`input-board-completion-comments` input</t>
+        </is>
+      </c>
+      <c r="D795" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E795" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'board completion comments'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F795" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G795" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H795" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B796" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C796" s="2" t="inlineStr">
+        <is>
+          <t>`input-completion-comments` input</t>
+        </is>
+      </c>
+      <c r="D796" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E796" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'completion comments'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F796" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G796" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H796" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B797" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C797" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-desc` input</t>
+        </is>
+      </c>
+      <c r="D797" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E797" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new desc'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F797" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G797" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H797" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B798" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C798" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-due` input</t>
+        </is>
+      </c>
+      <c r="D798" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E798" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new due'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F798" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G798" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H798" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B799" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C799" s="2" t="inlineStr">
+        <is>
+          <t>`input-new-title` input</t>
+        </is>
+      </c>
+      <c r="D799" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E799" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'new title'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F799" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G799" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H799" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B800" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C800" s="2" t="inlineStr">
+        <is>
+          <t>`input-subtask-title` input</t>
+        </is>
+      </c>
+      <c r="D800" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E800" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'subtask title'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F800" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G800" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H800" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B801" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C801" s="2" t="inlineStr">
+        <is>
+          <t>`input-task-search` input</t>
+        </is>
+      </c>
+      <c r="D801" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E801" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'task search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F801" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G801" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H801" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B802" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C802" s="2" t="inlineStr">
+        <is>
+          <t>`input-viewer-search` input</t>
+        </is>
+      </c>
+      <c r="D802" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E802" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'viewer search'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F802" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G802" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H802" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B803" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C803" s="2" t="inlineStr">
+        <is>
+          <t>`select-new-dept` selector</t>
+        </is>
+      </c>
+      <c r="D803" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E803" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'new dept'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F803" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G803" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H803" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B804" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C804" s="2" t="inlineStr">
+        <is>
+          <t>`select-new-priority` selector</t>
+        </is>
+      </c>
+      <c r="D804" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E804" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'new priority'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F804" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G804" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H804" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B805" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C805" s="2" t="inlineStr">
+        <is>
+          <t>`select-new-project` selector</t>
+        </is>
+      </c>
+      <c r="D805" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E805" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'new project'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F805" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G805" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H805" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B806" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C806" s="2" t="inlineStr">
+        <is>
+          <t>`select-new-status` selector</t>
+        </is>
+      </c>
+      <c r="D806" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E806" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'new status'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F806" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G806" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H806" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B807" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C807" s="2" t="inlineStr">
+        <is>
+          <t>`select-project-filter` selector</t>
+        </is>
+      </c>
+      <c r="D807" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E807" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'project filter'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F807" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G807" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H807" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="2" t="inlineStr">
+        <is>
+          <t>My Work Tasks</t>
+        </is>
+      </c>
+      <c r="B808" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/tasks</t>
+        </is>
+      </c>
+      <c r="C808" s="2" t="inlineStr">
+        <is>
+          <t>`select-subtask-priority` selector</t>
+        </is>
+      </c>
+      <c r="D808" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E808" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'subtask priority'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F808" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G808" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H808" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B809" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C809" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /api/meetings/{id}</t>
+        </is>
+      </c>
+      <c r="D809" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E809" s="2" t="inlineStr">
+        <is>
+          <t>Sends a DELETE to /api/meetings/{id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F809" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G809" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H809" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B810" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C810" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/meetings</t>
+        </is>
+      </c>
+      <c r="D810" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E810" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Meetings screen calls /api/meetings to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F810" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G810" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Meetings page.</t>
+        </is>
+      </c>
+      <c r="H810" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B811" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C811" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/meetings/webhook-status</t>
+        </is>
+      </c>
+      <c r="D811" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E811" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Meetings screen calls /api/meetings/webhook-status to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F811" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G811" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Meetings page.</t>
+        </is>
+      </c>
+      <c r="H811" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B812" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C812" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/mytool/company-priorities</t>
+        </is>
+      </c>
+      <c r="D812" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E812" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Meetings screen calls /api/mytool/company-priorities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F812" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G812" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Meetings page.</t>
+        </is>
+      </c>
+      <c r="H812" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B813" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C813" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pm-assignable-users</t>
+        </is>
+      </c>
+      <c r="D813" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E813" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Meetings screen calls /api/pm-assignable-users to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F813" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G813" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Meetings page.</t>
+        </is>
+      </c>
+      <c r="H813" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B814" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C814" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities</t>
+        </is>
+      </c>
+      <c r="D814" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E814" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Meetings screen calls /api/priorities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F814" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G814" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Meetings page.</t>
+        </is>
+      </c>
+      <c r="H814" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B815" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C815" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects</t>
+        </is>
+      </c>
+      <c r="D815" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E815" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Meetings screen calls /api/projects to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F815" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G815" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Meetings page.</t>
+        </is>
+      </c>
+      <c r="H815" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B816" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C816" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/meetings/action-items/{id}/dismiss</t>
+        </is>
+      </c>
+      <c r="D816" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E816" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/meetings/action-items/{id}/dismiss when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F816" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G816" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H816" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B817" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C817" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/meetings/action-items/{itemId}/{endpoint}</t>
+        </is>
+      </c>
+      <c r="D817" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E817" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/meetings/action-items/{itemId}/{endpoint} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F817" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G817" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H817" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B818" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C818" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/meetings/manual</t>
+        </is>
+      </c>
+      <c r="D818" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E818" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/meetings/manual when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F818" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G818" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H818" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B819" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C819" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/meetings/test-webhook</t>
+        </is>
+      </c>
+      <c r="D819" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E819" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/meetings/test-webhook when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F819" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G819" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H819" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B820" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C820" s="2" t="inlineStr">
+        <is>
+          <t>`button-add-action-item` button</t>
+        </is>
+      </c>
+      <c r="D820" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E820" s="2" t="inlineStr">
+        <is>
+          <t>'Add action item' button — triggers the 'add action item' action on the My Work Meetings screen.</t>
+        </is>
+      </c>
+      <c r="F820" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G820" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H820" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B821" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C821" s="2" t="inlineStr">
+        <is>
+          <t>`button-add-meeting` button</t>
+        </is>
+      </c>
+      <c r="D821" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E821" s="2" t="inlineStr">
+        <is>
+          <t>'Add meeting' button — triggers the 'add meeting' action on the My Work Meetings screen.</t>
+        </is>
+      </c>
+      <c r="F821" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G821" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H821" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B822" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C822" s="2" t="inlineStr">
+        <is>
+          <t>`button-cancel-convert` button</t>
+        </is>
+      </c>
+      <c r="D822" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E822" s="2" t="inlineStr">
+        <is>
+          <t>'Cancel convert' button — triggers the 'cancel convert' action on the My Work Meetings screen.</t>
+        </is>
+      </c>
+      <c r="F822" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G822" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H822" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B823" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C823" s="2" t="inlineStr">
+        <is>
+          <t>`button-cancel-manual` button</t>
+        </is>
+      </c>
+      <c r="D823" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E823" s="2" t="inlineStr">
+        <is>
+          <t>'Cancel manual' button — triggers the 'cancel manual' action on the My Work Meetings screen.</t>
+        </is>
+      </c>
+      <c r="F823" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G823" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H823" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B824" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C824" s="2" t="inlineStr">
+        <is>
+          <t>`button-close-webhook` button</t>
+        </is>
+      </c>
+      <c r="D824" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E824" s="2" t="inlineStr">
+        <is>
+          <t>'Close webhook' button — triggers the 'close webhook' action on the My Work Meetings screen.</t>
+        </is>
+      </c>
+      <c r="F824" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G824" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H824" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B825" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C825" s="2" t="inlineStr">
+        <is>
+          <t>`button-confirm-convert` button</t>
+        </is>
+      </c>
+      <c r="D825" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E825" s="2" t="inlineStr">
+        <is>
+          <t>'Confirm convert' button — triggers the 'confirm convert' action on the My Work Meetings screen.</t>
+        </is>
+      </c>
+      <c r="F825" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G825" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H825" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B826" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C826" s="2" t="inlineStr">
+        <is>
+          <t>`button-copy-webhook` button</t>
+        </is>
+      </c>
+      <c r="D826" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E826" s="2" t="inlineStr">
+        <is>
+          <t>'Copy webhook' button — triggers the 'copy webhook' action on the My Work Meetings screen.</t>
+        </is>
+      </c>
+      <c r="F826" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G826" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H826" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B827" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C827" s="2" t="inlineStr">
+        <is>
+          <t>`button-save-manual` button</t>
+        </is>
+      </c>
+      <c r="D827" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E827" s="2" t="inlineStr">
+        <is>
+          <t>'Save manual' button — triggers the 'save manual' action on the My Work Meetings screen.</t>
+        </is>
+      </c>
+      <c r="F827" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G827" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H827" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B828" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C828" s="2" t="inlineStr">
+        <is>
+          <t>`button-test-webhook` button</t>
+        </is>
+      </c>
+      <c r="D828" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E828" s="2" t="inlineStr">
+        <is>
+          <t>'Test webhook' button — triggers the 'test webhook' action on the My Work Meetings screen.</t>
+        </is>
+      </c>
+      <c r="F828" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G828" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H828" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B829" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C829" s="2" t="inlineStr">
+        <is>
+          <t>`button-webhook-setup` button</t>
+        </is>
+      </c>
+      <c r="D829" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E829" s="2" t="inlineStr">
+        <is>
+          <t>'Webhook setup' button — triggers the 'webhook setup' action on the My Work Meetings screen.</t>
+        </is>
+      </c>
+      <c r="F829" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G829" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H829" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B830" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C830" s="2" t="inlineStr">
+        <is>
+          <t>`input-convert-title` input</t>
+        </is>
+      </c>
+      <c r="D830" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E830" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'convert title'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F830" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G830" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H830" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B831" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C831" s="2" t="inlineStr">
+        <is>
+          <t>`input-manual-summary` input</t>
+        </is>
+      </c>
+      <c r="D831" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E831" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'manual summary'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F831" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G831" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H831" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B832" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C832" s="2" t="inlineStr">
+        <is>
+          <t>`input-manual-title` input</t>
+        </is>
+      </c>
+      <c r="D832" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E832" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'manual title'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F832" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G832" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H832" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B833" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C833" s="2" t="inlineStr">
+        <is>
+          <t>`input-planned-date` input</t>
+        </is>
+      </c>
+      <c r="D833" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E833" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'planned date'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F833" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G833" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H833" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B834" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C834" s="2" t="inlineStr">
+        <is>
+          <t>`input-project-name` input</t>
+        </is>
+      </c>
+      <c r="D834" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E834" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'project name'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F834" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G834" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H834" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B835" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C835" s="2" t="inlineStr">
+        <is>
+          <t>`input-size-kwp` input</t>
+        </is>
+      </c>
+      <c r="D835" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E835" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'size kwp'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F835" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G835" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H835" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B836" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C836" s="2" t="inlineStr">
+        <is>
+          <t>`input-webhook-url` input</t>
+        </is>
+      </c>
+      <c r="D836" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E836" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'webhook url'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F836" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G836" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H836" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B837" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C837" s="2" t="inlineStr">
+        <is>
+          <t>`select-department` selector</t>
+        </is>
+      </c>
+      <c r="D837" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E837" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'department'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F837" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G837" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H837" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B838" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C838" s="2" t="inlineStr">
+        <is>
+          <t>`select-horizon` selector</t>
+        </is>
+      </c>
+      <c r="D838" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E838" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'horizon'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F838" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G838" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H838" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B839" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C839" s="2" t="inlineStr">
+        <is>
+          <t>`select-pm` selector</t>
+        </is>
+      </c>
+      <c r="D839" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E839" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'pm'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F839" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G839" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H839" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B840" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C840" s="2" t="inlineStr">
+        <is>
+          <t>`select-priority` selector</t>
+        </is>
+      </c>
+      <c r="D840" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E840" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'priority'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F840" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G840" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H840" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B841" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C841" s="2" t="inlineStr">
+        <is>
+          <t>`select-priority-department` selector</t>
+        </is>
+      </c>
+      <c r="D841" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E841" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'priority department'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F841" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G841" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H841" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B842" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C842" s="2" t="inlineStr">
+        <is>
+          <t>`select-project-link` selector</t>
+        </is>
+      </c>
+      <c r="D842" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E842" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'project link'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F842" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G842" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H842" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="2" t="inlineStr">
+        <is>
+          <t>My Work Meetings</t>
+        </is>
+      </c>
+      <c r="B843" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/meetings</t>
+        </is>
+      </c>
+      <c r="C843" s="2" t="inlineStr">
+        <is>
+          <t>`select-severity` selector</t>
+        </is>
+      </c>
+      <c r="D843" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E843" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'severity'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F843" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G843" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H843" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="inlineStr">
+        <is>
+          <t>My Work Settings</t>
+        </is>
+      </c>
+      <c r="B844" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/settings</t>
+        </is>
+      </c>
+      <c r="C844" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/user/preferences</t>
+        </is>
+      </c>
+      <c r="D844" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E844" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Settings screen calls /api/user/preferences to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F844" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G844" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Settings page.</t>
+        </is>
+      </c>
+      <c r="H844" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="2" t="inlineStr">
+        <is>
+          <t>My Work Admin Settings</t>
+        </is>
+      </c>
+      <c r="B845" s="2" t="inlineStr">
+        <is>
+          <t>/admin/my-tool-settings</t>
+        </is>
+      </c>
+      <c r="C845" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /api/mytool/company-priorities/{id}</t>
+        </is>
+      </c>
+      <c r="D845" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E845" s="2" t="inlineStr">
+        <is>
+          <t>Sends a DELETE to /api/mytool/company-priorities/{id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F845" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G845" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H845" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="inlineStr">
+        <is>
+          <t>My Work Admin Settings</t>
+        </is>
+      </c>
+      <c r="B846" s="2" t="inlineStr">
+        <is>
+          <t>/admin/my-tool-settings</t>
+        </is>
+      </c>
+      <c r="C846" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/mytool/company-priorities</t>
+        </is>
+      </c>
+      <c r="D846" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E846" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Admin Settings screen calls /api/mytool/company-priorities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F846" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G846" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Admin Settings page.</t>
+        </is>
+      </c>
+      <c r="H846" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="2" t="inlineStr">
+        <is>
+          <t>My Work Admin Settings</t>
+        </is>
+      </c>
+      <c r="B847" s="2" t="inlineStr">
+        <is>
+          <t>/admin/my-tool-settings</t>
+        </is>
+      </c>
+      <c r="C847" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/mytool/settings</t>
+        </is>
+      </c>
+      <c r="D847" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E847" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Admin Settings screen calls /api/mytool/settings to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F847" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G847" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Admin Settings page.</t>
+        </is>
+      </c>
+      <c r="H847" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="inlineStr">
+        <is>
+          <t>My Work Admin Settings</t>
+        </is>
+      </c>
+      <c r="B848" s="2" t="inlineStr">
+        <is>
+          <t>/admin/my-tool-settings</t>
+        </is>
+      </c>
+      <c r="C848" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities</t>
+        </is>
+      </c>
+      <c r="D848" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E848" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Admin Settings screen calls /api/priorities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F848" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G848" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Admin Settings page.</t>
+        </is>
+      </c>
+      <c r="H848" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="2" t="inlineStr">
+        <is>
+          <t>My Work Admin Settings</t>
+        </is>
+      </c>
+      <c r="B849" s="2" t="inlineStr">
+        <is>
+          <t>/admin/my-tool-settings</t>
+        </is>
+      </c>
+      <c r="C849" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/mytool/company-priorities/{id}</t>
+        </is>
+      </c>
+      <c r="D849" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E849" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/mytool/company-priorities/{id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F849" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G849" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H849" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="inlineStr">
+        <is>
+          <t>My Work Admin Settings</t>
+        </is>
+      </c>
+      <c r="B850" s="2" t="inlineStr">
+        <is>
+          <t>/admin/my-tool-settings</t>
+        </is>
+      </c>
+      <c r="C850" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/mytool/company-priorities</t>
+        </is>
+      </c>
+      <c r="D850" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E850" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/mytool/company-priorities when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F850" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G850" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H850" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="2" t="inlineStr">
+        <is>
+          <t>My Work Admin Settings</t>
+        </is>
+      </c>
+      <c r="B851" s="2" t="inlineStr">
+        <is>
+          <t>/admin/my-tool-settings</t>
+        </is>
+      </c>
+      <c r="C851" s="2" t="inlineStr">
+        <is>
+          <t>PUT /api/mytool/settings</t>
+        </is>
+      </c>
+      <c r="D851" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E851" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PUT to /api/mytool/settings when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F851" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G851" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H851" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="inlineStr">
+        <is>
+          <t>My Work Admin Settings</t>
+        </is>
+      </c>
+      <c r="B852" s="2" t="inlineStr">
+        <is>
+          <t>/admin/my-tool-settings</t>
+        </is>
+      </c>
+      <c r="C852" s="2" t="inlineStr">
+        <is>
+          <t>`button-add-priority` button</t>
+        </is>
+      </c>
+      <c r="D852" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E852" s="2" t="inlineStr">
+        <is>
+          <t>'Add priority' button — triggers the 'add priority' action on the My Work Admin Settings screen.</t>
+        </is>
+      </c>
+      <c r="F852" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G852" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H852" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="2" t="inlineStr">
+        <is>
+          <t>My Work Admin Settings</t>
+        </is>
+      </c>
+      <c r="B853" s="2" t="inlineStr">
+        <is>
+          <t>/admin/my-tool-settings</t>
+        </is>
+      </c>
+      <c r="C853" s="2" t="inlineStr">
+        <is>
+          <t>`button-save-settings` button</t>
+        </is>
+      </c>
+      <c r="D853" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E853" s="2" t="inlineStr">
+        <is>
+          <t>'Save settings' button — triggers the 'save settings' action on the My Work Admin Settings screen.</t>
+        </is>
+      </c>
+      <c r="F853" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G853" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H853" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="inlineStr">
+        <is>
+          <t>My Work Admin Settings</t>
+        </is>
+      </c>
+      <c r="B854" s="2" t="inlineStr">
+        <is>
+          <t>/admin/my-tool-settings</t>
+        </is>
+      </c>
+      <c r="C854" s="2" t="inlineStr">
+        <is>
+          <t>`input-allowed-roles` input</t>
+        </is>
+      </c>
+      <c r="D854" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E854" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'allowed roles'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F854" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G854" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H854" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="2" t="inlineStr">
+        <is>
+          <t>My Work Admin Settings</t>
+        </is>
+      </c>
+      <c r="B855" s="2" t="inlineStr">
+        <is>
+          <t>/admin/my-tool-settings</t>
+        </is>
+      </c>
+      <c r="C855" s="2" t="inlineStr">
+        <is>
+          <t>`select-default-horizon` selector</t>
+        </is>
+      </c>
+      <c r="D855" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E855" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'default horizon'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F855" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G855" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H855" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B856" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C856" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /api/mytool/company-priorities/{id}</t>
+        </is>
+      </c>
+      <c r="D856" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E856" s="2" t="inlineStr">
+        <is>
+          <t>Sends a DELETE to /api/mytool/company-priorities/{id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F856" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G856" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H856" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B857" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C857" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/mytool/company-priorities</t>
+        </is>
+      </c>
+      <c r="D857" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E857" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Priorities screen calls /api/mytool/company-priorities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F857" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G857" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Priorities page.</t>
+        </is>
+      </c>
+      <c r="H857" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B858" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C858" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/mytool/company-priorities/{priorityId}/links</t>
+        </is>
+      </c>
+      <c r="D858" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E858" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Priorities screen calls /api/mytool/company-priorities/{priorityId}/links to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F858" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G858" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Priorities page.</t>
+        </is>
+      </c>
+      <c r="H858" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B859" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C859" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/mytool/priority-links/{linkId}</t>
+        </is>
+      </c>
+      <c r="D859" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E859" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Priorities screen calls /api/mytool/priority-links/{linkId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F859" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G859" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Priorities page.</t>
+        </is>
+      </c>
+      <c r="H859" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B860" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C860" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/operational-tasks-all</t>
+        </is>
+      </c>
+      <c r="D860" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E860" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Priorities screen calls /api/operational-tasks-all to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F860" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G860" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Priorities page.</t>
+        </is>
+      </c>
+      <c r="H860" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B861" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C861" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/operational-tasks/{encodeURIComponent(pn)}</t>
+        </is>
+      </c>
+      <c r="D861" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E861" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Priorities screen calls /api/operational-tasks/{encodeURIComponent(pn)} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F861" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G861" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Priorities page.</t>
+        </is>
+      </c>
+      <c r="H861" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B862" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C862" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities</t>
+        </is>
+      </c>
+      <c r="D862" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E862" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Priorities screen calls /api/priorities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F862" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G862" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Priorities page.</t>
+        </is>
+      </c>
+      <c r="H862" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B863" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C863" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects-summary</t>
+        </is>
+      </c>
+      <c r="D863" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E863" s="2" t="inlineStr">
+        <is>
+          <t>On load, the My Work Priorities screen calls /api/projects-summary to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F863" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G863" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the My Work Priorities page.</t>
+        </is>
+      </c>
+      <c r="H863" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B864" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C864" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/mytool/company-priorities/{editingPriority.id}</t>
+        </is>
+      </c>
+      <c r="D864" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E864" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/mytool/company-priorities/{editingPriority.id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F864" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G864" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H864" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B865" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C865" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/mytool/company-priorities/{id}</t>
+        </is>
+      </c>
+      <c r="D865" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E865" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/mytool/company-priorities/{id} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F865" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G865" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H865" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B866" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C866" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/mytool/company-priorities</t>
+        </is>
+      </c>
+      <c r="D866" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E866" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/mytool/company-priorities when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F866" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G866" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H866" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B867" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C867" s="2" t="inlineStr">
+        <is>
+          <t>`button-create-priority` button</t>
+        </is>
+      </c>
+      <c r="D867" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E867" s="2" t="inlineStr">
+        <is>
+          <t>'Create priority' button — triggers the 'create priority' action on the My Work Priorities screen.</t>
+        </is>
+      </c>
+      <c r="F867" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G867" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H867" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B868" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C868" s="2" t="inlineStr">
+        <is>
+          <t>`button-dialog-save` button</t>
+        </is>
+      </c>
+      <c r="D868" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E868" s="2" t="inlineStr">
+        <is>
+          <t>'Dialog save' button — triggers the 'dialog save' action on the My Work Priorities screen.</t>
+        </is>
+      </c>
+      <c r="F868" s="2" t="inlineStr">
+        <is>
+          <t>Depends on the action; typically triggers a mutation or navigation (see Data Sources).</t>
+        </is>
+      </c>
+      <c r="G868" s="2" t="inlineStr">
+        <is>
+          <t>Varies — some close dialogs, some save, some navigate. See the page source for the exact onClick.</t>
+        </is>
+      </c>
+      <c r="H868" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B869" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C869" s="2" t="inlineStr">
+        <is>
+          <t>`input-dialog-assigned` input</t>
+        </is>
+      </c>
+      <c r="D869" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E869" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'dialog assigned'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F869" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G869" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H869" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B870" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C870" s="2" t="inlineStr">
+        <is>
+          <t>`input-dialog-department` input</t>
+        </is>
+      </c>
+      <c r="D870" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E870" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'dialog department'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F870" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G870" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H870" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B871" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C871" s="2" t="inlineStr">
+        <is>
+          <t>`input-dialog-description` input</t>
+        </is>
+      </c>
+      <c r="D871" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E871" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'dialog description'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F871" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G871" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H871" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B872" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C872" s="2" t="inlineStr">
+        <is>
+          <t>`input-dialog-dod` input</t>
+        </is>
+      </c>
+      <c r="D872" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E872" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'dialog dod'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F872" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G872" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H872" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B873" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C873" s="2" t="inlineStr">
+        <is>
+          <t>`input-dialog-duedate` input</t>
+        </is>
+      </c>
+      <c r="D873" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E873" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'dialog duedate'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F873" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G873" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H873" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B874" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C874" s="2" t="inlineStr">
+        <is>
+          <t>`input-dialog-next-action` input</t>
+        </is>
+      </c>
+      <c r="D874" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E874" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'dialog next action'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F874" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G874" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H874" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B875" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C875" s="2" t="inlineStr">
+        <is>
+          <t>`input-dialog-rank` input</t>
+        </is>
+      </c>
+      <c r="D875" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E875" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'dialog rank'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F875" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G875" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H875" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B876" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C876" s="2" t="inlineStr">
+        <is>
+          <t>`input-dialog-support` input</t>
+        </is>
+      </c>
+      <c r="D876" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E876" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'dialog support'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F876" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G876" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H876" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B877" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C877" s="2" t="inlineStr">
+        <is>
+          <t>`input-dialog-title` input</t>
+        </is>
+      </c>
+      <c r="D877" s="2" t="inlineStr">
+        <is>
+          <t>Form field</t>
+        </is>
+      </c>
+      <c r="E877" s="2" t="inlineStr">
+        <is>
+          <t>Input for 'dialog title'. Captures the value to be submitted.</t>
+        </is>
+      </c>
+      <c r="F877" s="2" t="inlineStr">
+        <is>
+          <t>Submitted as part of a form mutation.</t>
+        </is>
+      </c>
+      <c r="G877" s="2" t="inlineStr">
+        <is>
+          <t>N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H877" s="2" t="inlineStr">
+        <is>
+          <t>Saved by the parent form's mutation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B878" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C878" s="2" t="inlineStr">
+        <is>
+          <t>`select-dialog-status` selector</t>
+        </is>
+      </c>
+      <c r="D878" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E878" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'dialog status'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F878" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G878" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H878" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B879" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C879" s="2" t="inlineStr">
+        <is>
+          <t>`select-link-project` selector</t>
+        </is>
+      </c>
+      <c r="D879" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E879" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'link project'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F879" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G879" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H879" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B880" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C880" s="2" t="inlineStr">
+        <is>
+          <t>`select-link-task` selector</t>
+        </is>
+      </c>
+      <c r="D880" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E880" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'link task'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F880" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G880" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H880" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="2" t="inlineStr">
+        <is>
+          <t>My Work Priorities</t>
+        </is>
+      </c>
+      <c r="B881" s="2" t="inlineStr">
+        <is>
+          <t>/my-work/priorities</t>
+        </is>
+      </c>
+      <c r="C881" s="2" t="inlineStr">
+        <is>
+          <t>`select-status-filter` selector</t>
+        </is>
+      </c>
+      <c r="D881" s="2" t="inlineStr">
+        <is>
+          <t>Form field / Filter</t>
+        </is>
+      </c>
+      <c r="E881" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown for 'status filter'. Either filters the list client-side or captures a choice to submit.</t>
+        </is>
+      </c>
+      <c r="F881" s="2" t="inlineStr">
+        <is>
+          <t>Client-side filter, or submitted as part of a form.</t>
+        </is>
+      </c>
+      <c r="G881" s="2" t="inlineStr">
+        <is>
+          <t>Re-renders or N/A until submit.</t>
+        </is>
+      </c>
+      <c r="H881" s="2" t="inlineStr">
+        <is>
+          <t>See parent action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="inlineStr">
+        <is>
+          <t>Priorities</t>
+        </is>
+      </c>
+      <c r="B882" s="2" t="inlineStr">
+        <is>
+          <t>/priorities</t>
+        </is>
+      </c>
+      <c r="C882" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities</t>
+        </is>
+      </c>
+      <c r="D882" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E882" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priorities screen calls /api/priorities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F882" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G882" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priorities page.</t>
+        </is>
+      </c>
+      <c r="H882" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="2" t="inlineStr">
+        <is>
+          <t>Priorities</t>
+        </is>
+      </c>
+      <c r="B883" s="2" t="inlineStr">
+        <is>
+          <t>/priorities</t>
+        </is>
+      </c>
+      <c r="C883" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities?{params}</t>
+        </is>
+      </c>
+      <c r="D883" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E883" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priorities screen calls /api/priorities?{params} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F883" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G883" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priorities page.</t>
+        </is>
+      </c>
+      <c r="H883" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="inlineStr">
+        <is>
+          <t>Priorities</t>
+        </is>
+      </c>
+      <c r="B884" s="2" t="inlineStr">
+        <is>
+          <t>/priorities</t>
+        </is>
+      </c>
+      <c r="C884" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/users</t>
+        </is>
+      </c>
+      <c r="D884" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E884" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priorities screen calls /api/users to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F884" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G884" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priorities page.</t>
+        </is>
+      </c>
+      <c r="H884" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="2" t="inlineStr">
+        <is>
+          <t>Priorities</t>
+        </is>
+      </c>
+      <c r="B885" s="2" t="inlineStr">
+        <is>
+          <t>/priorities</t>
+        </is>
+      </c>
+      <c r="C885" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/users-list-for-priority</t>
+        </is>
+      </c>
+      <c r="D885" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E885" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priorities screen calls /api/users-list-for-priority to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F885" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G885" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priorities page.</t>
+        </is>
+      </c>
+      <c r="H885" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="inlineStr">
+        <is>
+          <t>Priorities</t>
+        </is>
+      </c>
+      <c r="B886" s="2" t="inlineStr">
+        <is>
+          <t>/priorities</t>
+        </is>
+      </c>
+      <c r="C886" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/priorities/{priorityId}</t>
+        </is>
+      </c>
+      <c r="D886" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E886" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PATCH to /api/priorities/{priorityId} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F886" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G886" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H886" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="inlineStr">
+        <is>
+          <t>Priorities</t>
+        </is>
+      </c>
+      <c r="B887" s="2" t="inlineStr">
+        <is>
+          <t>/priorities</t>
+        </is>
+      </c>
+      <c r="C887" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/priorities</t>
+        </is>
+      </c>
+      <c r="D887" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E887" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/priorities when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F887" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G887" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H887" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="inlineStr">
+        <is>
+          <t>Priorities</t>
+        </is>
+      </c>
+      <c r="B888" s="2" t="inlineStr">
+        <is>
+          <t>/priorities</t>
+        </is>
+      </c>
+      <c r="C888" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/priorities/{priorityId}/escalate</t>
+        </is>
+      </c>
+      <c r="D888" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E888" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/priorities/{priorityId}/escalate when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F888" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G888" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H888" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B889" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C889" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /api/priorities/{priorityId}/projects/{projectId}</t>
+        </is>
+      </c>
+      <c r="D889" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E889" s="2" t="inlineStr">
+        <is>
+          <t>Sends a DELETE to /api/priorities/{priorityId}/projects/{projectId} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F889" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G889" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H889" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B890" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C890" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/mytool/company-priorities</t>
+        </is>
+      </c>
+      <c r="D890" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E890" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priority Detail screen calls /api/mytool/company-priorities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F890" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G890" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priority Detail page.</t>
+        </is>
+      </c>
+      <c r="H890" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B891" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C891" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities</t>
+        </is>
+      </c>
+      <c r="D891" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E891" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priority Detail screen calls /api/priorities to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F891" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G891" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priority Detail page.</t>
+        </is>
+      </c>
+      <c r="H891" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B892" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C892" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities/{priorityId}</t>
+        </is>
+      </c>
+      <c r="D892" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E892" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priority Detail screen calls /api/priorities/{priorityId} to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F892" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G892" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priority Detail page.</t>
+        </is>
+      </c>
+      <c r="H892" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B893" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C893" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities/{priorityId}/approvals</t>
+        </is>
+      </c>
+      <c r="D893" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E893" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priority Detail screen calls /api/priorities/{priorityId}/approvals to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F893" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G893" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priority Detail page.</t>
+        </is>
+      </c>
+      <c r="H893" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B894" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C894" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities/{priorityId}/break-down</t>
+        </is>
+      </c>
+      <c r="D894" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E894" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priority Detail screen calls /api/priorities/{priorityId}/break-down to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F894" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G894" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priority Detail page.</t>
+        </is>
+      </c>
+      <c r="H894" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B895" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C895" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities/{priorityId}/children</t>
+        </is>
+      </c>
+      <c r="D895" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E895" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priority Detail screen calls /api/priorities/{priorityId}/children to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F895" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G895" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priority Detail page.</t>
+        </is>
+      </c>
+      <c r="H895" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B896" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C896" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities/{priorityId}/escalate</t>
+        </is>
+      </c>
+      <c r="D896" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E896" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priority Detail screen calls /api/priorities/{priorityId}/escalate to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F896" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G896" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priority Detail page.</t>
+        </is>
+      </c>
+      <c r="H896" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B897" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C897" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities/{priorityId}/tasks</t>
+        </is>
+      </c>
+      <c r="D897" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E897" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priority Detail screen calls /api/priorities/{priorityId}/tasks to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F897" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G897" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priority Detail page.</t>
+        </is>
+      </c>
+      <c r="H897" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B898" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C898" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/priorities/{priorityId}/updates</t>
+        </is>
+      </c>
+      <c r="D898" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E898" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priority Detail screen calls /api/priorities/{priorityId}/updates to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F898" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G898" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priority Detail page.</t>
+        </is>
+      </c>
+      <c r="H898" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B899" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C899" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects-summary</t>
+        </is>
+      </c>
+      <c r="D899" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E899" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priority Detail screen calls /api/projects-summary to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F899" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G899" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priority Detail page.</t>
+        </is>
+      </c>
+      <c r="H899" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B900" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C900" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/v2/projects</t>
+        </is>
+      </c>
+      <c r="D900" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E900" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priority Detail screen calls /api/v2/projects to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F900" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G900" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priority Detail page.</t>
+        </is>
+      </c>
+      <c r="H900" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B901" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C901" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/v2/projects?pageSize=500</t>
+        </is>
+      </c>
+      <c r="D901" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E901" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Priority Detail screen calls /api/v2/projects?pageSize=500 to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F901" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G901" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Priority Detail page.</t>
+        </is>
+      </c>
+      <c r="H901" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B902" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C902" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/priorities/{priorityId}/projects</t>
+        </is>
+      </c>
+      <c r="D902" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E902" s="2" t="inlineStr">
+        <is>
+          <t>Sends a POST to /api/priorities/{priorityId}/projects when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F902" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G902" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H902" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="2" t="inlineStr">
+        <is>
+          <t>Priority Detail</t>
+        </is>
+      </c>
+      <c r="B903" s="2" t="inlineStr">
+        <is>
+          <t>/priorities/:id</t>
+        </is>
+      </c>
+      <c r="C903" s="2" t="inlineStr">
+        <is>
+          <t>PUT /api/priorities/{priorityId}</t>
+        </is>
+      </c>
+      <c r="D903" s="2" t="inlineStr">
+        <is>
+          <t>Mutation</t>
+        </is>
+      </c>
+      <c r="E903" s="2" t="inlineStr">
+        <is>
+          <t>Sends a PUT to /api/priorities/{priorityId} when the user saves / triggers an action on this screen.</t>
+        </is>
+      </c>
+      <c r="F903" s="2" t="inlineStr">
+        <is>
+          <t>Writes to the server.</t>
+        </is>
+      </c>
+      <c r="G903" s="2" t="inlineStr">
+        <is>
+          <t>Usually re-queries the affected lists on success, shows a toast.</t>
+        </is>
+      </c>
+      <c r="H903" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="inlineStr">
+        <is>
+          <t>Action Launchpad</t>
+        </is>
+      </c>
+      <c r="B904" s="2" t="inlineStr">
+        <is>
+          <t>/actions/launchpad</t>
+        </is>
+      </c>
+      <c r="C904" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/eng/tasks</t>
+        </is>
+      </c>
+      <c r="D904" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E904" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Action Launchpad screen calls /api/eng/tasks to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F904" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G904" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Action Launchpad page.</t>
+        </is>
+      </c>
+      <c r="H904" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="2" t="inlineStr">
+        <is>
+          <t>Action Launchpad</t>
+        </is>
+      </c>
+      <c r="B905" s="2" t="inlineStr">
+        <is>
+          <t>/actions/launchpad</t>
+        </is>
+      </c>
+      <c r="C905" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pm-otg/projects</t>
+        </is>
+      </c>
+      <c r="D905" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E905" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Action Launchpad screen calls /api/pm-otg/projects to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F905" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G905" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Action Launchpad page.</t>
+        </is>
+      </c>
+      <c r="H905" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="inlineStr">
+        <is>
+          <t>Action Launchpad</t>
+        </is>
+      </c>
+      <c r="B906" s="2" t="inlineStr">
+        <is>
+          <t>/actions/launchpad</t>
+        </is>
+      </c>
+      <c r="C906" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pm-otg/projects/{projectId}/generate-po</t>
+        </is>
+      </c>
+      <c r="D906" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E906" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Action Launchpad screen calls /api/pm-otg/projects/{projectId}/generate-po to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F906" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G906" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Action Launchpad page.</t>
+        </is>
+      </c>
+      <c r="H906" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="2" t="inlineStr">
+        <is>
+          <t>Action Launchpad</t>
+        </is>
+      </c>
+      <c r="B907" s="2" t="inlineStr">
+        <is>
+          <t>/actions/launchpad</t>
+        </is>
+      </c>
+      <c r="C907" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/pm-otg/projects/{projectId}/link-invoice</t>
+        </is>
+      </c>
+      <c r="D907" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E907" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Action Launchpad screen calls /api/pm-otg/projects/{projectId}/link-invoice to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F907" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G907" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Action Launchpad page.</t>
+        </is>
+      </c>
+      <c r="H907" s="2" t="inlineStr">
+        <is>
+          <t>See Data Sources sheet for the handler + tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="inlineStr">
+        <is>
+          <t>Action Launchpad</t>
+        </is>
+      </c>
+      <c r="B908" s="2" t="inlineStr">
+        <is>
+          <t>/actions/launchpad</t>
+        </is>
+      </c>
+      <c r="C908" s="2" t="inlineStr">
+        <is>
+          <t>(page load) GET /api/projects-summary</t>
+        </is>
+      </c>
+      <c r="D908" s="2" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E908" s="2" t="inlineStr">
+        <is>
+          <t>On load, the Action Launchpad screen calls /api/projects-summary to fetch data it needs to render.</t>
+        </is>
+      </c>
+      <c r="F908" s="2" t="inlineStr">
+        <is>
+          <t>Read from the server.</t>
+        </is>
+      </c>
+      <c r="G908" s="2" t="inlineStr">
+        <is>
+          <t>Populates a section of the Action Launchpad page.</t>
+        </is>
+      </c>
+      <c r="H908" s="2" t="inlineStr">
         <is>
           <t>See Data Sources sheet for the handler + tables.</t>
         </is>
